--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -589,45 +589,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>22/02/2026</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
@@ -1286,10 +1286,10 @@
         <v>0</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2295,45 +2295,45 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>22/02/2026</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
@@ -3516,45 +3516,45 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>22/02/2026</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4677,45 +4677,45 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>22/02/2026</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5838,45 +5838,45 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>22/02/2026</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr"/>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6999,45 +6999,45 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>22/02/2026</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr"/>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="I138" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -649,45 +649,49 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>17/31</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -798,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -849,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -952,7 +956,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -1290,22 +1294,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1372,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1450,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1524,22 +1528,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -1602,17 +1606,17 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
@@ -1680,22 +1684,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -2364,45 +2368,49 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -3574,45 +3582,49 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4739,45 +4751,49 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5904,45 +5920,49 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7069,45 +7089,49 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8168,45 +8168,45 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="inlineStr"/>
-      <c r="H164" s="6" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9329,45 +9329,45 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G191" s="6" t="inlineStr"/>
-      <c r="H191" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10490,45 +10490,45 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D218" s="6" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F218" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G218" s="6" t="inlineStr"/>
-      <c r="H218" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I218" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11651,45 +11651,45 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B245" s="6" t="inlineStr">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C245" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D245" s="6" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F245" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G245" s="6" t="inlineStr"/>
-      <c r="H245" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I245" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12812,45 +12812,45 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B272" s="6" t="inlineStr">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C272" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D272" s="6" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F272" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G272" s="6" t="inlineStr"/>
-      <c r="H272" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I272" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13973,45 +13973,45 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B299" s="6" t="inlineStr">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C299" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D299" s="6" t="inlineStr">
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F299" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G299" s="6" t="inlineStr"/>
-      <c r="H299" s="6" t="inlineStr">
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I299" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -956,7 +956,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>26</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>26</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -1996,22 +1996,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>26</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -2074,22 +2074,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>26</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -2152,22 +2152,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>26</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -9329,45 +9329,49 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E191" s="4" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10490,45 +10494,49 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E218" s="4" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I218" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11651,45 +11659,49 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E245" s="4" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I245" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12812,45 +12824,49 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E272" s="4" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I272" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13973,45 +13989,49 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="inlineStr">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D299" s="2" t="inlineStr">
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E299" s="2" t="inlineStr">
+      <c r="E299" s="4" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F299" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G299" s="2" t="inlineStr"/>
-      <c r="H299" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I299" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H299" s="4" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+      <c r="I299" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
         <v>1</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         <v>1</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         <v>1</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         <v>1</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         <v>1</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8211,45 +8211,45 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G165" s="6" t="inlineStr"/>
-      <c r="H165" s="6" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9376,45 +9376,45 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C192" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr"/>
-      <c r="H192" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I192" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10541,45 +10541,45 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D219" s="6" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G219" s="6" t="inlineStr"/>
-      <c r="H219" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I219" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11706,45 +11706,45 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B246" s="6" t="inlineStr">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C246" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D246" s="6" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F246" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G246" s="6" t="inlineStr"/>
-      <c r="H246" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I246" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12871,45 +12871,45 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B273" s="6" t="inlineStr">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C273" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D273" s="6" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F273" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G273" s="6" t="inlineStr"/>
-      <c r="H273" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I273" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14036,45 +14036,45 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B300" s="6" t="inlineStr">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C300" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D300" s="6" t="inlineStr">
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="2" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F300" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G300" s="6" t="inlineStr"/>
-      <c r="H300" s="6" t="inlineStr">
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I300" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -956,7 +956,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -1918,17 +1918,17 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
@@ -1996,22 +1996,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -2074,22 +2074,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -2152,22 +2152,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>25</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -9376,45 +9376,49 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10541,45 +10545,49 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E219" s="4" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I219" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11706,45 +11714,49 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E246" s="4" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I246" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12871,45 +12883,49 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B273" s="2" t="inlineStr">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E273" s="4" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I273" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14036,45 +14052,49 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E300" s="2" t="inlineStr">
+      <c r="E300" s="4" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F300" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G300" s="2" t="inlineStr"/>
-      <c r="H300" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I300" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I300" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1843,10 +1843,10 @@
         <v>2</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         <v>2</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         <v>2</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         <v>2</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         <v>2</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8254,45 +8254,45 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G166" s="6" t="inlineStr"/>
-      <c r="H166" s="6" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>0/0</t>
         </is>
       </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9423,45 +9423,45 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C193" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D193" s="6" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G193" s="6" t="inlineStr"/>
-      <c r="H193" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10592,45 +10592,45 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B220" s="6" t="inlineStr">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C220" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G220" s="6" t="inlineStr"/>
-      <c r="H220" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I220" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11761,45 +11761,45 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B247" s="6" t="inlineStr">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C247" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D247" s="6" t="inlineStr">
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F247" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G247" s="6" t="inlineStr"/>
-      <c r="H247" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I247" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12930,45 +12930,45 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B274" s="6" t="inlineStr">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C274" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D274" s="6" t="inlineStr">
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F274" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G274" s="6" t="inlineStr"/>
-      <c r="H274" s="6" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I274" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14099,45 +14099,45 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B301" s="6" t="inlineStr">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C301" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D301" s="6" t="inlineStr">
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="E301" s="2" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F301" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G301" s="6" t="inlineStr"/>
-      <c r="H301" s="6" t="inlineStr">
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr"/>
+      <c r="H301" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I301" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -956,7 +956,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>84.4%</t>
         </is>
       </c>
     </row>
@@ -1996,22 +1996,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -2074,22 +2074,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -2152,22 +2152,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.3%</t>
         </is>
       </c>
     </row>
@@ -9423,45 +9423,49 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E193" s="4" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10592,45 +10596,49 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E220" s="4" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I220" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11761,45 +11769,49 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E247" s="4" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I247" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12930,45 +12942,49 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E274" s="4" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I274" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14099,45 +14115,49 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="inlineStr">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D301" s="2" t="inlineStr">
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="E301" s="4" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F301" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G301" s="2" t="inlineStr"/>
-      <c r="H301" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I301" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+      <c r="I301" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -577,7 +577,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>18/30</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>17/30</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -737,7 +737,7 @@
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -788,7 +788,7 @@
       <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -839,7 +839,7 @@
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -890,7 +890,7 @@
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -941,7 +941,7 @@
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       <c r="G11" s="6" t="inlineStr"/>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1090,7 +1090,7 @@
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="G13" s="6" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1181,7 +1181,7 @@
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="M15" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="5" t="n">
         <v>27</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1425,7 +1425,7 @@
       <c r="G17" s="6" t="inlineStr"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="M17" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N17" s="5" t="n">
         <v>27</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.3%</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="M18" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>27</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="M19" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N19" s="5" t="n">
         <v>27</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="M20" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>27</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1756,28 +1756,28 @@
         </is>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N21" s="5" t="n">
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>24</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="M22" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>27</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       <c r="G23" s="6" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="M23" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N23" s="5" t="n">
         <v>27</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>85.1%</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="M24" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>27</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="M25" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>27</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/30</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -3525,7 +3525,7 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/31</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       <c r="G59" s="6" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -3705,7 +3705,7 @@
       <c r="G60" s="6" t="inlineStr"/>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
@@ -3748,7 +3748,7 @@
       <c r="G61" s="6" t="inlineStr"/>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -3791,7 +3791,7 @@
       <c r="G62" s="6" t="inlineStr"/>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -3834,7 +3834,7 @@
       <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -3877,7 +3877,7 @@
       <c r="G64" s="6" t="inlineStr"/>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
@@ -3920,7 +3920,7 @@
       <c r="G65" s="6" t="inlineStr"/>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -3963,7 +3963,7 @@
       <c r="G66" s="6" t="inlineStr"/>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
@@ -4006,7 +4006,7 @@
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
@@ -4049,7 +4049,7 @@
       <c r="G68" s="6" t="inlineStr"/>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
@@ -4092,7 +4092,7 @@
       <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
@@ -4135,7 +4135,7 @@
       <c r="G70" s="6" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
@@ -4178,7 +4178,7 @@
       <c r="G71" s="6" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -4221,7 +4221,7 @@
       <c r="G72" s="6" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -4264,7 +4264,7 @@
       <c r="G73" s="6" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -4307,7 +4307,7 @@
       <c r="G74" s="6" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -4350,7 +4350,7 @@
       <c r="G75" s="6" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
@@ -4393,7 +4393,7 @@
       <c r="G76" s="6" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
@@ -4436,7 +4436,7 @@
       <c r="G77" s="6" t="inlineStr"/>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
@@ -4479,7 +4479,7 @@
       <c r="G78" s="6" t="inlineStr"/>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="G79" s="6" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -4565,7 +4565,7 @@
       <c r="G80" s="6" t="inlineStr"/>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
@@ -4608,7 +4608,7 @@
       <c r="G81" s="6" t="inlineStr"/>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -4651,7 +4651,7 @@
       <c r="G82" s="6" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -4694,7 +4694,7 @@
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/28</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/28</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4831,7 +4831,7 @@
       <c r="G86" s="6" t="inlineStr"/>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -4874,7 +4874,7 @@
       <c r="G87" s="6" t="inlineStr"/>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
@@ -4917,7 +4917,7 @@
       <c r="G88" s="6" t="inlineStr"/>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
@@ -4960,7 +4960,7 @@
       <c r="G89" s="6" t="inlineStr"/>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -5003,7 +5003,7 @@
       <c r="G90" s="6" t="inlineStr"/>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
@@ -5046,7 +5046,7 @@
       <c r="G91" s="6" t="inlineStr"/>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -5089,7 +5089,7 @@
       <c r="G92" s="6" t="inlineStr"/>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
@@ -5132,7 +5132,7 @@
       <c r="G93" s="6" t="inlineStr"/>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -5175,7 +5175,7 @@
       <c r="G94" s="6" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
@@ -5218,7 +5218,7 @@
       <c r="G95" s="6" t="inlineStr"/>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
@@ -5261,7 +5261,7 @@
       <c r="G96" s="6" t="inlineStr"/>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
@@ -5304,7 +5304,7 @@
       <c r="G97" s="6" t="inlineStr"/>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -5347,7 +5347,7 @@
       <c r="G98" s="6" t="inlineStr"/>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
@@ -5390,7 +5390,7 @@
       <c r="G99" s="6" t="inlineStr"/>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -5433,7 +5433,7 @@
       <c r="G100" s="6" t="inlineStr"/>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
@@ -5476,7 +5476,7 @@
       <c r="G101" s="6" t="inlineStr"/>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -5519,7 +5519,7 @@
       <c r="G102" s="6" t="inlineStr"/>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="G103" s="6" t="inlineStr"/>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
@@ -5605,7 +5605,7 @@
       <c r="G104" s="6" t="inlineStr"/>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
@@ -5648,7 +5648,7 @@
       <c r="G105" s="6" t="inlineStr"/>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
@@ -5691,7 +5691,7 @@
       <c r="G106" s="6" t="inlineStr"/>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
@@ -5734,7 +5734,7 @@
       <c r="G107" s="6" t="inlineStr"/>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
@@ -5777,7 +5777,7 @@
       <c r="G108" s="6" t="inlineStr"/>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
@@ -5820,7 +5820,7 @@
       <c r="G109" s="6" t="inlineStr"/>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
@@ -5863,7 +5863,7 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -6000,7 +6000,7 @@
       <c r="G113" s="6" t="inlineStr"/>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
@@ -6043,7 +6043,7 @@
       <c r="G114" s="6" t="inlineStr"/>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
@@ -6086,7 +6086,7 @@
       <c r="G115" s="6" t="inlineStr"/>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
@@ -6129,7 +6129,7 @@
       <c r="G116" s="6" t="inlineStr"/>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I116" s="6" t="inlineStr">
@@ -6172,7 +6172,7 @@
       <c r="G117" s="6" t="inlineStr"/>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
@@ -6215,7 +6215,7 @@
       <c r="G118" s="6" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I118" s="6" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="G119" s="6" t="inlineStr"/>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
@@ -6301,7 +6301,7 @@
       <c r="G120" s="6" t="inlineStr"/>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
@@ -6344,7 +6344,7 @@
       <c r="G121" s="6" t="inlineStr"/>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
@@ -6387,7 +6387,7 @@
       <c r="G122" s="6" t="inlineStr"/>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
@@ -6430,7 +6430,7 @@
       <c r="G123" s="6" t="inlineStr"/>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
@@ -6473,7 +6473,7 @@
       <c r="G124" s="6" t="inlineStr"/>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
@@ -6516,7 +6516,7 @@
       <c r="G125" s="6" t="inlineStr"/>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
@@ -6559,7 +6559,7 @@
       <c r="G126" s="6" t="inlineStr"/>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
@@ -6602,7 +6602,7 @@
       <c r="G127" s="6" t="inlineStr"/>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
@@ -6645,7 +6645,7 @@
       <c r="G128" s="6" t="inlineStr"/>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I128" s="6" t="inlineStr">
@@ -6688,7 +6688,7 @@
       <c r="G129" s="6" t="inlineStr"/>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
@@ -6731,7 +6731,7 @@
       <c r="G130" s="6" t="inlineStr"/>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
@@ -6774,7 +6774,7 @@
       <c r="G131" s="6" t="inlineStr"/>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
@@ -6817,7 +6817,7 @@
       <c r="G132" s="6" t="inlineStr"/>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
@@ -6860,7 +6860,7 @@
       <c r="G133" s="6" t="inlineStr"/>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
@@ -6903,7 +6903,7 @@
       <c r="G134" s="6" t="inlineStr"/>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
@@ -6946,7 +6946,7 @@
       <c r="G135" s="6" t="inlineStr"/>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
@@ -6989,7 +6989,7 @@
       <c r="G136" s="6" t="inlineStr"/>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
@@ -7032,7 +7032,7 @@
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/29</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -7169,7 +7169,7 @@
       <c r="G140" s="6" t="inlineStr"/>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
@@ -7212,7 +7212,7 @@
       <c r="G141" s="6" t="inlineStr"/>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
@@ -7255,7 +7255,7 @@
       <c r="G142" s="6" t="inlineStr"/>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I142" s="6" t="inlineStr">
@@ -7298,7 +7298,7 @@
       <c r="G143" s="6" t="inlineStr"/>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
@@ -7341,7 +7341,7 @@
       <c r="G144" s="6" t="inlineStr"/>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
@@ -7384,7 +7384,7 @@
       <c r="G145" s="6" t="inlineStr"/>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
@@ -7427,7 +7427,7 @@
       <c r="G146" s="6" t="inlineStr"/>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
@@ -7470,7 +7470,7 @@
       <c r="G147" s="6" t="inlineStr"/>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I147" s="6" t="inlineStr">
@@ -7513,7 +7513,7 @@
       <c r="G148" s="6" t="inlineStr"/>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I148" s="6" t="inlineStr">
@@ -7556,7 +7556,7 @@
       <c r="G149" s="6" t="inlineStr"/>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I149" s="6" t="inlineStr">
@@ -7599,7 +7599,7 @@
       <c r="G150" s="6" t="inlineStr"/>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I150" s="6" t="inlineStr">
@@ -7642,7 +7642,7 @@
       <c r="G151" s="6" t="inlineStr"/>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr">
@@ -7685,7 +7685,7 @@
       <c r="G152" s="6" t="inlineStr"/>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I152" s="6" t="inlineStr">
@@ -7728,7 +7728,7 @@
       <c r="G153" s="6" t="inlineStr"/>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I153" s="6" t="inlineStr">
@@ -7771,7 +7771,7 @@
       <c r="G154" s="6" t="inlineStr"/>
       <c r="H154" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I154" s="6" t="inlineStr">
@@ -7814,7 +7814,7 @@
       <c r="G155" s="6" t="inlineStr"/>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I155" s="6" t="inlineStr">
@@ -7857,7 +7857,7 @@
       <c r="G156" s="6" t="inlineStr"/>
       <c r="H156" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I156" s="6" t="inlineStr">
@@ -7900,7 +7900,7 @@
       <c r="G157" s="6" t="inlineStr"/>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I157" s="6" t="inlineStr">
@@ -7943,7 +7943,7 @@
       <c r="G158" s="6" t="inlineStr"/>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I158" s="6" t="inlineStr">
@@ -7986,7 +7986,7 @@
       <c r="G159" s="6" t="inlineStr"/>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
@@ -8029,7 +8029,7 @@
       <c r="G160" s="6" t="inlineStr"/>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I160" s="6" t="inlineStr">
@@ -8072,7 +8072,7 @@
       <c r="G161" s="6" t="inlineStr"/>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
@@ -8115,7 +8115,7 @@
       <c r="G162" s="6" t="inlineStr"/>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I162" s="6" t="inlineStr">
@@ -8158,7 +8158,7 @@
       <c r="G163" s="6" t="inlineStr"/>
       <c r="H163" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I163" s="6" t="inlineStr">
@@ -8168,131 +8168,143 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="4" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="4" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E166" s="4" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8342,7 @@
       <c r="G167" s="6" t="inlineStr"/>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I167" s="6" t="inlineStr">
@@ -8373,7 +8385,7 @@
       <c r="G168" s="6" t="inlineStr"/>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I168" s="6" t="inlineStr">
@@ -8416,7 +8428,7 @@
       <c r="G169" s="6" t="inlineStr"/>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I169" s="6" t="inlineStr">
@@ -8459,7 +8471,7 @@
       <c r="G170" s="6" t="inlineStr"/>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I170" s="6" t="inlineStr">
@@ -8502,7 +8514,7 @@
       <c r="G171" s="6" t="inlineStr"/>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
@@ -8545,7 +8557,7 @@
       <c r="G172" s="6" t="inlineStr"/>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I172" s="6" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="G173" s="6" t="inlineStr"/>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I173" s="6" t="inlineStr">
@@ -8631,7 +8643,7 @@
       <c r="G174" s="6" t="inlineStr"/>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I174" s="6" t="inlineStr">
@@ -8674,7 +8686,7 @@
       <c r="G175" s="6" t="inlineStr"/>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I175" s="6" t="inlineStr">
@@ -8717,7 +8729,7 @@
       <c r="G176" s="6" t="inlineStr"/>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I176" s="6" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="G177" s="6" t="inlineStr"/>
       <c r="H177" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I177" s="6" t="inlineStr">
@@ -8803,7 +8815,7 @@
       <c r="G178" s="6" t="inlineStr"/>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I178" s="6" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="G179" s="6" t="inlineStr"/>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I179" s="6" t="inlineStr">
@@ -8889,7 +8901,7 @@
       <c r="G180" s="6" t="inlineStr"/>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I180" s="6" t="inlineStr">
@@ -8932,7 +8944,7 @@
       <c r="G181" s="6" t="inlineStr"/>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I181" s="6" t="inlineStr">
@@ -8975,7 +8987,7 @@
       <c r="G182" s="6" t="inlineStr"/>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I182" s="6" t="inlineStr">
@@ -9018,7 +9030,7 @@
       <c r="G183" s="6" t="inlineStr"/>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I183" s="6" t="inlineStr">
@@ -9061,7 +9073,7 @@
       <c r="G184" s="6" t="inlineStr"/>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I184" s="6" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="G185" s="6" t="inlineStr"/>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I185" s="6" t="inlineStr">
@@ -9147,7 +9159,7 @@
       <c r="G186" s="6" t="inlineStr"/>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I186" s="6" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="G187" s="6" t="inlineStr"/>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I187" s="6" t="inlineStr">
@@ -9233,7 +9245,7 @@
       <c r="G188" s="6" t="inlineStr"/>
       <c r="H188" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I188" s="6" t="inlineStr">
@@ -9276,7 +9288,7 @@
       <c r="G189" s="6" t="inlineStr"/>
       <c r="H189" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I189" s="6" t="inlineStr">
@@ -9319,7 +9331,7 @@
       <c r="G190" s="6" t="inlineStr"/>
       <c r="H190" s="6" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I190" s="6" t="inlineStr">
@@ -9366,7 +9378,7 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/32</t>
         </is>
       </c>
       <c r="I191" s="4" t="inlineStr">
@@ -9413,7 +9425,7 @@
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/32</t>
         </is>
       </c>
       <c r="I192" s="4" t="inlineStr">
@@ -9460,7 +9472,7 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/32</t>
         </is>
       </c>
       <c r="I193" s="4" t="inlineStr">
@@ -9503,7 +9515,7 @@
       <c r="G194" s="6" t="inlineStr"/>
       <c r="H194" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I194" s="6" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="G195" s="6" t="inlineStr"/>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I195" s="6" t="inlineStr">
@@ -9589,7 +9601,7 @@
       <c r="G196" s="6" t="inlineStr"/>
       <c r="H196" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I196" s="6" t="inlineStr">
@@ -9632,7 +9644,7 @@
       <c r="G197" s="6" t="inlineStr"/>
       <c r="H197" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I197" s="6" t="inlineStr">
@@ -9675,7 +9687,7 @@
       <c r="G198" s="6" t="inlineStr"/>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I198" s="6" t="inlineStr">
@@ -9718,7 +9730,7 @@
       <c r="G199" s="6" t="inlineStr"/>
       <c r="H199" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I199" s="6" t="inlineStr">
@@ -9761,7 +9773,7 @@
       <c r="G200" s="6" t="inlineStr"/>
       <c r="H200" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I200" s="6" t="inlineStr">
@@ -9804,7 +9816,7 @@
       <c r="G201" s="6" t="inlineStr"/>
       <c r="H201" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I201" s="6" t="inlineStr">
@@ -9847,7 +9859,7 @@
       <c r="G202" s="6" t="inlineStr"/>
       <c r="H202" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I202" s="6" t="inlineStr">
@@ -9890,7 +9902,7 @@
       <c r="G203" s="6" t="inlineStr"/>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I203" s="6" t="inlineStr">
@@ -9933,7 +9945,7 @@
       <c r="G204" s="6" t="inlineStr"/>
       <c r="H204" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I204" s="6" t="inlineStr">
@@ -9976,7 +9988,7 @@
       <c r="G205" s="6" t="inlineStr"/>
       <c r="H205" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I205" s="6" t="inlineStr">
@@ -10019,7 +10031,7 @@
       <c r="G206" s="6" t="inlineStr"/>
       <c r="H206" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I206" s="6" t="inlineStr">
@@ -10062,7 +10074,7 @@
       <c r="G207" s="6" t="inlineStr"/>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I207" s="6" t="inlineStr">
@@ -10105,7 +10117,7 @@
       <c r="G208" s="6" t="inlineStr"/>
       <c r="H208" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I208" s="6" t="inlineStr">
@@ -10148,7 +10160,7 @@
       <c r="G209" s="6" t="inlineStr"/>
       <c r="H209" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I209" s="6" t="inlineStr">
@@ -10191,7 +10203,7 @@
       <c r="G210" s="6" t="inlineStr"/>
       <c r="H210" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I210" s="6" t="inlineStr">
@@ -10234,7 +10246,7 @@
       <c r="G211" s="6" t="inlineStr"/>
       <c r="H211" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I211" s="6" t="inlineStr">
@@ -10277,7 +10289,7 @@
       <c r="G212" s="6" t="inlineStr"/>
       <c r="H212" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I212" s="6" t="inlineStr">
@@ -10320,7 +10332,7 @@
       <c r="G213" s="6" t="inlineStr"/>
       <c r="H213" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I213" s="6" t="inlineStr">
@@ -10363,7 +10375,7 @@
       <c r="G214" s="6" t="inlineStr"/>
       <c r="H214" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I214" s="6" t="inlineStr">
@@ -10406,7 +10418,7 @@
       <c r="G215" s="6" t="inlineStr"/>
       <c r="H215" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I215" s="6" t="inlineStr">
@@ -10449,7 +10461,7 @@
       <c r="G216" s="6" t="inlineStr"/>
       <c r="H216" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I216" s="6" t="inlineStr">
@@ -10492,7 +10504,7 @@
       <c r="G217" s="6" t="inlineStr"/>
       <c r="H217" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I217" s="6" t="inlineStr">
@@ -10539,7 +10551,7 @@
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/29</t>
         </is>
       </c>
       <c r="I218" s="4" t="inlineStr">
@@ -10586,7 +10598,7 @@
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/29</t>
         </is>
       </c>
       <c r="I219" s="4" t="inlineStr">
@@ -10633,7 +10645,7 @@
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I220" s="4" t="inlineStr">
@@ -10676,7 +10688,7 @@
       <c r="G221" s="6" t="inlineStr"/>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I221" s="6" t="inlineStr">
@@ -10719,7 +10731,7 @@
       <c r="G222" s="6" t="inlineStr"/>
       <c r="H222" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I222" s="6" t="inlineStr">
@@ -10762,7 +10774,7 @@
       <c r="G223" s="6" t="inlineStr"/>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I223" s="6" t="inlineStr">
@@ -10805,7 +10817,7 @@
       <c r="G224" s="6" t="inlineStr"/>
       <c r="H224" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I224" s="6" t="inlineStr">
@@ -10848,7 +10860,7 @@
       <c r="G225" s="6" t="inlineStr"/>
       <c r="H225" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I225" s="6" t="inlineStr">
@@ -10891,7 +10903,7 @@
       <c r="G226" s="6" t="inlineStr"/>
       <c r="H226" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I226" s="6" t="inlineStr">
@@ -10934,7 +10946,7 @@
       <c r="G227" s="6" t="inlineStr"/>
       <c r="H227" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I227" s="6" t="inlineStr">
@@ -10977,7 +10989,7 @@
       <c r="G228" s="6" t="inlineStr"/>
       <c r="H228" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I228" s="6" t="inlineStr">
@@ -11020,7 +11032,7 @@
       <c r="G229" s="6" t="inlineStr"/>
       <c r="H229" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I229" s="6" t="inlineStr">
@@ -11063,7 +11075,7 @@
       <c r="G230" s="6" t="inlineStr"/>
       <c r="H230" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I230" s="6" t="inlineStr">
@@ -11106,7 +11118,7 @@
       <c r="G231" s="6" t="inlineStr"/>
       <c r="H231" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I231" s="6" t="inlineStr">
@@ -11149,7 +11161,7 @@
       <c r="G232" s="6" t="inlineStr"/>
       <c r="H232" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I232" s="6" t="inlineStr">
@@ -11192,7 +11204,7 @@
       <c r="G233" s="6" t="inlineStr"/>
       <c r="H233" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I233" s="6" t="inlineStr">
@@ -11235,7 +11247,7 @@
       <c r="G234" s="6" t="inlineStr"/>
       <c r="H234" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I234" s="6" t="inlineStr">
@@ -11278,7 +11290,7 @@
       <c r="G235" s="6" t="inlineStr"/>
       <c r="H235" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I235" s="6" t="inlineStr">
@@ -11321,7 +11333,7 @@
       <c r="G236" s="6" t="inlineStr"/>
       <c r="H236" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I236" s="6" t="inlineStr">
@@ -11364,7 +11376,7 @@
       <c r="G237" s="6" t="inlineStr"/>
       <c r="H237" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I237" s="6" t="inlineStr">
@@ -11407,7 +11419,7 @@
       <c r="G238" s="6" t="inlineStr"/>
       <c r="H238" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I238" s="6" t="inlineStr">
@@ -11450,7 +11462,7 @@
       <c r="G239" s="6" t="inlineStr"/>
       <c r="H239" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I239" s="6" t="inlineStr">
@@ -11493,7 +11505,7 @@
       <c r="G240" s="6" t="inlineStr"/>
       <c r="H240" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I240" s="6" t="inlineStr">
@@ -11536,7 +11548,7 @@
       <c r="G241" s="6" t="inlineStr"/>
       <c r="H241" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I241" s="6" t="inlineStr">
@@ -11579,7 +11591,7 @@
       <c r="G242" s="6" t="inlineStr"/>
       <c r="H242" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I242" s="6" t="inlineStr">
@@ -11622,7 +11634,7 @@
       <c r="G243" s="6" t="inlineStr"/>
       <c r="H243" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I243" s="6" t="inlineStr">
@@ -11665,7 +11677,7 @@
       <c r="G244" s="6" t="inlineStr"/>
       <c r="H244" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I244" s="6" t="inlineStr">
@@ -11712,7 +11724,7 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
       <c r="I245" s="4" t="inlineStr">
@@ -11759,7 +11771,7 @@
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
       <c r="I246" s="4" t="inlineStr">
@@ -11806,7 +11818,7 @@
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I247" s="4" t="inlineStr">
@@ -11849,7 +11861,7 @@
       <c r="G248" s="6" t="inlineStr"/>
       <c r="H248" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I248" s="6" t="inlineStr">
@@ -11892,7 +11904,7 @@
       <c r="G249" s="6" t="inlineStr"/>
       <c r="H249" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I249" s="6" t="inlineStr">
@@ -11935,7 +11947,7 @@
       <c r="G250" s="6" t="inlineStr"/>
       <c r="H250" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I250" s="6" t="inlineStr">
@@ -11978,7 +11990,7 @@
       <c r="G251" s="6" t="inlineStr"/>
       <c r="H251" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I251" s="6" t="inlineStr">
@@ -12021,7 +12033,7 @@
       <c r="G252" s="6" t="inlineStr"/>
       <c r="H252" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I252" s="6" t="inlineStr">
@@ -12064,7 +12076,7 @@
       <c r="G253" s="6" t="inlineStr"/>
       <c r="H253" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I253" s="6" t="inlineStr">
@@ -12107,7 +12119,7 @@
       <c r="G254" s="6" t="inlineStr"/>
       <c r="H254" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I254" s="6" t="inlineStr">
@@ -12150,7 +12162,7 @@
       <c r="G255" s="6" t="inlineStr"/>
       <c r="H255" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I255" s="6" t="inlineStr">
@@ -12193,7 +12205,7 @@
       <c r="G256" s="6" t="inlineStr"/>
       <c r="H256" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I256" s="6" t="inlineStr">
@@ -12236,7 +12248,7 @@
       <c r="G257" s="6" t="inlineStr"/>
       <c r="H257" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I257" s="6" t="inlineStr">
@@ -12279,7 +12291,7 @@
       <c r="G258" s="6" t="inlineStr"/>
       <c r="H258" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I258" s="6" t="inlineStr">
@@ -12322,7 +12334,7 @@
       <c r="G259" s="6" t="inlineStr"/>
       <c r="H259" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I259" s="6" t="inlineStr">
@@ -12365,7 +12377,7 @@
       <c r="G260" s="6" t="inlineStr"/>
       <c r="H260" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I260" s="6" t="inlineStr">
@@ -12408,7 +12420,7 @@
       <c r="G261" s="6" t="inlineStr"/>
       <c r="H261" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I261" s="6" t="inlineStr">
@@ -12451,7 +12463,7 @@
       <c r="G262" s="6" t="inlineStr"/>
       <c r="H262" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I262" s="6" t="inlineStr">
@@ -12494,7 +12506,7 @@
       <c r="G263" s="6" t="inlineStr"/>
       <c r="H263" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I263" s="6" t="inlineStr">
@@ -12537,7 +12549,7 @@
       <c r="G264" s="6" t="inlineStr"/>
       <c r="H264" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I264" s="6" t="inlineStr">
@@ -12580,7 +12592,7 @@
       <c r="G265" s="6" t="inlineStr"/>
       <c r="H265" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I265" s="6" t="inlineStr">
@@ -12623,7 +12635,7 @@
       <c r="G266" s="6" t="inlineStr"/>
       <c r="H266" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I266" s="6" t="inlineStr">
@@ -12666,7 +12678,7 @@
       <c r="G267" s="6" t="inlineStr"/>
       <c r="H267" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I267" s="6" t="inlineStr">
@@ -12709,7 +12721,7 @@
       <c r="G268" s="6" t="inlineStr"/>
       <c r="H268" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I268" s="6" t="inlineStr">
@@ -12752,7 +12764,7 @@
       <c r="G269" s="6" t="inlineStr"/>
       <c r="H269" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I269" s="6" t="inlineStr">
@@ -12795,7 +12807,7 @@
       <c r="G270" s="6" t="inlineStr"/>
       <c r="H270" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I270" s="6" t="inlineStr">
@@ -12838,7 +12850,7 @@
       <c r="G271" s="6" t="inlineStr"/>
       <c r="H271" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I271" s="6" t="inlineStr">
@@ -12885,7 +12897,7 @@
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr">
@@ -12932,7 +12944,7 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr">
@@ -12979,7 +12991,7 @@
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/31</t>
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr">
@@ -13022,7 +13034,7 @@
       <c r="G275" s="6" t="inlineStr"/>
       <c r="H275" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I275" s="6" t="inlineStr">
@@ -13065,7 +13077,7 @@
       <c r="G276" s="6" t="inlineStr"/>
       <c r="H276" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I276" s="6" t="inlineStr">
@@ -13108,7 +13120,7 @@
       <c r="G277" s="6" t="inlineStr"/>
       <c r="H277" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I277" s="6" t="inlineStr">
@@ -13151,7 +13163,7 @@
       <c r="G278" s="6" t="inlineStr"/>
       <c r="H278" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I278" s="6" t="inlineStr">
@@ -13194,7 +13206,7 @@
       <c r="G279" s="6" t="inlineStr"/>
       <c r="H279" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I279" s="6" t="inlineStr">
@@ -13237,7 +13249,7 @@
       <c r="G280" s="6" t="inlineStr"/>
       <c r="H280" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I280" s="6" t="inlineStr">
@@ -13280,7 +13292,7 @@
       <c r="G281" s="6" t="inlineStr"/>
       <c r="H281" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I281" s="6" t="inlineStr">
@@ -13323,7 +13335,7 @@
       <c r="G282" s="6" t="inlineStr"/>
       <c r="H282" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I282" s="6" t="inlineStr">
@@ -13366,7 +13378,7 @@
       <c r="G283" s="6" t="inlineStr"/>
       <c r="H283" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I283" s="6" t="inlineStr">
@@ -13409,7 +13421,7 @@
       <c r="G284" s="6" t="inlineStr"/>
       <c r="H284" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I284" s="6" t="inlineStr">
@@ -13452,7 +13464,7 @@
       <c r="G285" s="6" t="inlineStr"/>
       <c r="H285" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I285" s="6" t="inlineStr">
@@ -13495,7 +13507,7 @@
       <c r="G286" s="6" t="inlineStr"/>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
@@ -13538,7 +13550,7 @@
       <c r="G287" s="6" t="inlineStr"/>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
@@ -13581,7 +13593,7 @@
       <c r="G288" s="6" t="inlineStr"/>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
@@ -13624,7 +13636,7 @@
       <c r="G289" s="6" t="inlineStr"/>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
@@ -13667,7 +13679,7 @@
       <c r="G290" s="6" t="inlineStr"/>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
@@ -13710,7 +13722,7 @@
       <c r="G291" s="6" t="inlineStr"/>
       <c r="H291" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I291" s="6" t="inlineStr">
@@ -13753,7 +13765,7 @@
       <c r="G292" s="6" t="inlineStr"/>
       <c r="H292" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I292" s="6" t="inlineStr">
@@ -13796,7 +13808,7 @@
       <c r="G293" s="6" t="inlineStr"/>
       <c r="H293" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I293" s="6" t="inlineStr">
@@ -13839,7 +13851,7 @@
       <c r="G294" s="6" t="inlineStr"/>
       <c r="H294" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I294" s="6" t="inlineStr">
@@ -13882,7 +13894,7 @@
       <c r="G295" s="6" t="inlineStr"/>
       <c r="H295" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I295" s="6" t="inlineStr">
@@ -13925,7 +13937,7 @@
       <c r="G296" s="6" t="inlineStr"/>
       <c r="H296" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I296" s="6" t="inlineStr">
@@ -13968,7 +13980,7 @@
       <c r="G297" s="6" t="inlineStr"/>
       <c r="H297" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
@@ -14011,7 +14023,7 @@
       <c r="G298" s="6" t="inlineStr"/>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">
@@ -14058,7 +14070,7 @@
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -704,45 +704,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
@@ -1297,10 +1297,10 @@
         <v>2</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         <v>2</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>2</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         <v>2</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1609,10 +1609,10 @@
         <v>2</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>2</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2430,45 +2430,45 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -3629,45 +3629,45 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4798,45 +4798,45 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5967,45 +5967,45 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr"/>
-      <c r="H113" s="6" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7136,45 +7136,45 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -577,7 +577,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/29</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -737,7 +737,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       <c r="G6" s="6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -839,7 +839,7 @@
       <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -890,7 +890,7 @@
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -941,7 +941,7 @@
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -994,7 +994,7 @@
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.6%</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       <c r="G11" s="6" t="inlineStr"/>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1090,7 +1090,7 @@
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="G13" s="6" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1181,7 +1181,7 @@
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="M15" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N15" s="5" t="n">
         <v>27</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1425,7 +1425,7 @@
       <c r="G17" s="6" t="inlineStr"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1503,7 +1503,7 @@
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1581,7 +1581,7 @@
       <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1659,7 +1659,7 @@
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1737,7 +1737,7 @@
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1815,7 +1815,7 @@
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1893,7 +1893,7 @@
       <c r="G23" s="6" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1971,7 +1971,7 @@
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -2049,7 +2049,7 @@
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="M25" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>27</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -2205,7 +2205,7 @@
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>24/32</t>
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>20/32</t>
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>23/32</t>
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr">
@@ -13034,7 +13034,7 @@
       <c r="G275" s="6" t="inlineStr"/>
       <c r="H275" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I275" s="6" t="inlineStr">
@@ -13077,7 +13077,7 @@
       <c r="G276" s="6" t="inlineStr"/>
       <c r="H276" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I276" s="6" t="inlineStr">
@@ -13120,7 +13120,7 @@
       <c r="G277" s="6" t="inlineStr"/>
       <c r="H277" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I277" s="6" t="inlineStr">
@@ -13163,7 +13163,7 @@
       <c r="G278" s="6" t="inlineStr"/>
       <c r="H278" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I278" s="6" t="inlineStr">
@@ -13206,7 +13206,7 @@
       <c r="G279" s="6" t="inlineStr"/>
       <c r="H279" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I279" s="6" t="inlineStr">
@@ -13249,7 +13249,7 @@
       <c r="G280" s="6" t="inlineStr"/>
       <c r="H280" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I280" s="6" t="inlineStr">
@@ -13292,7 +13292,7 @@
       <c r="G281" s="6" t="inlineStr"/>
       <c r="H281" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I281" s="6" t="inlineStr">
@@ -13335,7 +13335,7 @@
       <c r="G282" s="6" t="inlineStr"/>
       <c r="H282" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I282" s="6" t="inlineStr">
@@ -13378,7 +13378,7 @@
       <c r="G283" s="6" t="inlineStr"/>
       <c r="H283" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I283" s="6" t="inlineStr">
@@ -13421,7 +13421,7 @@
       <c r="G284" s="6" t="inlineStr"/>
       <c r="H284" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I284" s="6" t="inlineStr">
@@ -13464,7 +13464,7 @@
       <c r="G285" s="6" t="inlineStr"/>
       <c r="H285" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I285" s="6" t="inlineStr">
@@ -13507,7 +13507,7 @@
       <c r="G286" s="6" t="inlineStr"/>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
@@ -13550,7 +13550,7 @@
       <c r="G287" s="6" t="inlineStr"/>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
@@ -13593,7 +13593,7 @@
       <c r="G288" s="6" t="inlineStr"/>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
@@ -13636,7 +13636,7 @@
       <c r="G289" s="6" t="inlineStr"/>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
@@ -13679,7 +13679,7 @@
       <c r="G290" s="6" t="inlineStr"/>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
@@ -13722,7 +13722,7 @@
       <c r="G291" s="6" t="inlineStr"/>
       <c r="H291" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I291" s="6" t="inlineStr">
@@ -13765,7 +13765,7 @@
       <c r="G292" s="6" t="inlineStr"/>
       <c r="H292" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I292" s="6" t="inlineStr">
@@ -13808,7 +13808,7 @@
       <c r="G293" s="6" t="inlineStr"/>
       <c r="H293" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I293" s="6" t="inlineStr">
@@ -13851,7 +13851,7 @@
       <c r="G294" s="6" t="inlineStr"/>
       <c r="H294" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I294" s="6" t="inlineStr">
@@ -13894,7 +13894,7 @@
       <c r="G295" s="6" t="inlineStr"/>
       <c r="H295" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I295" s="6" t="inlineStr">
@@ -13937,7 +13937,7 @@
       <c r="G296" s="6" t="inlineStr"/>
       <c r="H296" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I296" s="6" t="inlineStr">
@@ -13980,7 +13980,7 @@
       <c r="G297" s="6" t="inlineStr"/>
       <c r="H297" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
@@ -14023,7 +14023,7 @@
       <c r="G298" s="6" t="inlineStr"/>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -704,45 +704,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -802,7 +806,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +857,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -956,7 +960,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1013,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
     </row>
@@ -1294,22 +1298,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -1372,22 +1376,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -1450,22 +1454,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>78.5%</t>
         </is>
       </c>
     </row>
@@ -1528,22 +1532,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -1606,22 +1610,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -1684,22 +1688,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -2430,45 +2434,49 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -3629,45 +3637,49 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4798,45 +4810,49 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5967,45 +5983,49 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>16/31</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7136,45 +7156,49 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -759,45 +759,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -1301,10 +1301,10 @@
         <v>3</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
         <v>3</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         <v>3</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
         <v>3</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         <v>3</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         <v>3</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2496,45 +2496,45 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -3684,45 +3684,45 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4857,45 +4857,45 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6030,45 +6030,45 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7203,45 +7203,45 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr"/>
-      <c r="H141" s="6" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -759,45 +759,49 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -806,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -857,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +964,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -1298,22 +1302,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1380,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
@@ -1454,22 +1458,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -1532,22 +1536,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1614,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -1688,22 +1692,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -2496,45 +2500,49 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -3684,45 +3692,49 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>25/31</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4857,45 +4869,49 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6030,45 +6046,49 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7203,45 +7223,49 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E141" s="4" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,45 +814,45 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
@@ -1305,10 +1305,10 @@
         <v>4</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
         <v>4</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
         <v>4</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         <v>4</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         <v>4</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
         <v>4</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2562,45 +2562,45 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3739,45 +3739,45 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr"/>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4916,45 +4916,45 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6093,45 +6093,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr"/>
-      <c r="H115" s="6" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7270,45 +7270,45 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,49 +810,53 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -861,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +968,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1021,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.5%</t>
         </is>
       </c>
     </row>
@@ -1302,22 +1306,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -1380,22 +1384,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
     </row>
@@ -1458,22 +1462,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1540,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -1614,22 +1618,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -1692,22 +1696,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -2562,45 +2566,49 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3739,45 +3747,49 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4916,45 +4928,49 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6093,45 +6109,49 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7270,45 +7290,49 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E142" s="4" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
@@ -1777,10 +1777,10 @@
         <v>3</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>3</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
         <v>3</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         <v>3</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>3</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         <v>3</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8381,45 +8381,45 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G167" s="6" t="inlineStr"/>
-      <c r="H167" s="6" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9554,45 +9554,45 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G194" s="6" t="inlineStr"/>
-      <c r="H194" s="6" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I194" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10727,45 +10727,45 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D221" s="6" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G221" s="6" t="inlineStr"/>
-      <c r="H221" s="6" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I221" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11900,45 +11900,45 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B248" s="6" t="inlineStr">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C248" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D248" s="6" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F248" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G248" s="6" t="inlineStr"/>
-      <c r="H248" s="6" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I248" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13073,45 +13073,45 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C275" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D275" s="6" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F275" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G275" s="6" t="inlineStr"/>
-      <c r="H275" s="6" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I275" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14246,45 +14246,45 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B302" s="6" t="inlineStr">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C302" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D302" s="6" t="inlineStr">
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F302" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G302" s="6" t="inlineStr"/>
-      <c r="H302" s="6" t="inlineStr">
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr"/>
+      <c r="H302" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I302" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -1774,22 +1774,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>60.3%</t>
         </is>
       </c>
     </row>
@@ -1852,22 +1852,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -1930,22 +1930,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
     </row>
@@ -2008,22 +2008,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>79.0%</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>23</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -8381,45 +8381,49 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9554,45 +9558,49 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E194" s="4" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>14/32</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10727,45 +10735,49 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E221" s="4" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I221" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11900,45 +11912,49 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E248" s="4" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I248" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>28/31</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13073,45 +13089,49 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E275" s="4" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I275" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>24/32</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14246,45 +14266,49 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="inlineStr">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D302" s="2" t="inlineStr">
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E302" s="2" t="inlineStr">
+      <c r="E302" s="4" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F302" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G302" s="2" t="inlineStr"/>
-      <c r="H302" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H302" s="4" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+      <c r="I302" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9">
@@ -1777,10 +1777,10 @@
         <v>4</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>4</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
         <v>4</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         <v>4</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>4</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8428,45 +8428,45 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G168" s="6" t="inlineStr"/>
-      <c r="H168" s="6" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9605,45 +9605,45 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F195" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G195" s="6" t="inlineStr"/>
-      <c r="H195" s="6" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I195" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10782,45 +10782,45 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B222" s="6" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C222" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D222" s="6" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G222" s="6" t="inlineStr"/>
-      <c r="H222" s="6" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I222" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11959,45 +11959,45 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B249" s="6" t="inlineStr">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C249" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D249" s="6" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F249" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G249" s="6" t="inlineStr"/>
-      <c r="H249" s="6" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I249" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13136,45 +13136,45 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B276" s="6" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C276" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D276" s="6" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F276" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G276" s="6" t="inlineStr"/>
-      <c r="H276" s="6" t="inlineStr">
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I276" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14313,45 +14313,45 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="6" t="inlineStr">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C303" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="6" t="inlineStr">
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="E303" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F303" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="6" t="inlineStr"/>
-      <c r="H303" s="6" t="inlineStr">
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I303" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
     </row>
@@ -1774,22 +1774,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -1852,22 +1852,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -1930,22 +1930,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>80.7%</t>
         </is>
       </c>
     </row>
@@ -2008,22 +2008,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>22</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -8428,45 +8428,49 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9605,45 +9609,49 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E195" s="4" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>11/32</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10782,45 +10790,49 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E222" s="4" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11959,45 +11971,49 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E249" s="4" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I249" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>13/31</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13136,45 +13152,49 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B276" s="2" t="inlineStr">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E276" s="4" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I276" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>1/32</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
@@ -1777,10 +1777,10 @@
         <v>5</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>5</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
         <v>5</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         <v>5</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>5</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8475,45 +8475,45 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="6" t="inlineStr"/>
-      <c r="H169" s="6" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I169" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9656,45 +9656,45 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F196" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="6" t="inlineStr"/>
-      <c r="H196" s="6" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I196" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10837,45 +10837,45 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C223" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="6" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="6" t="inlineStr"/>
-      <c r="H223" s="6" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I223" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12018,45 +12018,45 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="6" t="inlineStr">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C250" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="6" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F250" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="6" t="inlineStr"/>
-      <c r="H250" s="6" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I250" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13199,45 +13199,45 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="6" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C277" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="6" t="inlineStr">
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F277" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="6" t="inlineStr"/>
-      <c r="H277" s="6" t="inlineStr">
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I277" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14376,45 +14376,45 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="6" t="inlineStr">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C304" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="6" t="inlineStr">
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="E304" s="2" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F304" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="6" t="inlineStr"/>
-      <c r="H304" s="6" t="inlineStr">
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr"/>
+      <c r="H304" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I304" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.5%</t>
         </is>
       </c>
     </row>
@@ -1774,22 +1774,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -1852,22 +1852,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -1930,22 +1930,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
@@ -2008,22 +2008,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>21</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -8475,45 +8475,49 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E169" s="4" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9656,45 +9660,49 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E196" s="4" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>14/32</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10837,45 +10845,49 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E223" s="4" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I223" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12018,45 +12030,49 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E250" s="4" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I250" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>21/31</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13199,45 +13215,49 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B277" s="2" t="inlineStr">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E277" s="4" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I277" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>23/32</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14376,45 +14396,49 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D304" s="2" t="inlineStr">
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E304" s="2" t="inlineStr">
+      <c r="E304" s="4" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F304" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G304" s="2" t="inlineStr"/>
-      <c r="H304" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I304" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G304" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H304" s="4" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+      <c r="I304" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,49 +865,49 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
@@ -1309,10 +1309,10 @@
         <v>5</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         <v>5</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         <v>5</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         <v>5</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         <v>5</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         <v>5</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2613,45 +2613,45 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3794,45 +3794,45 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4975,45 +4975,45 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6156,45 +6156,45 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7337,45 +7337,45 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="inlineStr"/>
-      <c r="H143" s="6" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -865,49 +865,53 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -968,7 +972,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -1306,22 +1310,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -1384,22 +1388,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1466,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -1540,22 +1544,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>78.0%</t>
         </is>
       </c>
     </row>
@@ -1618,22 +1622,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1700,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -2613,45 +2617,49 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3794,45 +3802,49 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>17/31</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4975,45 +4987,49 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6156,45 +6172,49 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>19/31</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7337,45 +7357,49 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E143" s="4" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,49 +920,49 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1313,10 +1313,10 @@
         <v>6</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         <v>6</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         <v>6</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1547,10 +1547,10 @@
         <v>6</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1625,10 +1625,10 @@
         <v>6</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         <v>6</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2664,45 +2664,45 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3849,45 +3849,45 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr"/>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5034,45 +5034,45 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6219,45 +6219,45 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr"/>
-      <c r="H117" s="6" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7404,45 +7404,45 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -924,45 +924,49 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -972,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1029,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -1310,22 +1314,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -1388,22 +1392,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.5%</t>
         </is>
       </c>
     </row>
@@ -1466,22 +1470,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -1544,22 +1548,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1626,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -1700,22 +1704,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -2664,45 +2668,49 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3849,45 +3857,49 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>21/31</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5034,45 +5046,49 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6219,45 +6235,49 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>21/31</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7404,45 +7424,49 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -981,45 +981,45 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1317,10 +1317,10 @@
         <v>7</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         <v>7</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         <v>7</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         <v>7</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         <v>7</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1707,10 +1707,10 @@
         <v>7</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2715,45 +2715,45 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3904,45 +3904,45 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5093,45 +5093,45 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr"/>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6282,45 +6282,45 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7471,45 +7471,45 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G145" s="6" t="inlineStr"/>
-      <c r="H145" s="6" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -976,50 +976,54 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1029,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -1314,22 +1318,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1396,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1470,22 +1474,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1552,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -1626,22 +1630,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -1704,22 +1708,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -2715,45 +2719,49 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3904,45 +3912,49 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5093,45 +5105,49 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6282,45 +6298,49 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E118" s="4" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7471,45 +7491,49 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E145" s="4" t="inlineStr">
         <is>
           <t>09/03/2026</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>6</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         <v>6</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
         <v>6</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>6</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         <v>6</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         <v>5</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8594,45 +8594,45 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G170" s="6" t="inlineStr"/>
-      <c r="H170" s="6" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9779,45 +9779,45 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G197" s="6" t="inlineStr"/>
-      <c r="H197" s="6" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I197" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10964,45 +10964,45 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B224" s="6" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C224" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D224" s="6" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G224" s="6" t="inlineStr"/>
-      <c r="H224" s="6" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I224" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12149,45 +12149,45 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C251" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D251" s="6" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F251" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G251" s="6" t="inlineStr"/>
-      <c r="H251" s="6" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I251" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13334,45 +13334,45 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B278" s="6" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C278" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D278" s="6" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F278" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G278" s="6" t="inlineStr"/>
-      <c r="H278" s="6" t="inlineStr">
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I278" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14515,45 +14515,45 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B305" s="6" t="inlineStr">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C305" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D305" s="6" t="inlineStr">
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="E305" s="2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F305" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G305" s="6" t="inlineStr"/>
-      <c r="H305" s="6" t="inlineStr">
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr"/>
+      <c r="H305" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I305" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -1864,22 +1864,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -1942,22 +1942,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>80.3%</t>
         </is>
       </c>
     </row>
@@ -2020,22 +2020,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -2098,22 +2098,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -2176,22 +2176,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>20</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -8594,45 +8594,49 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E170" s="4" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9779,45 +9783,49 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E197" s="4" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>16/32</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10964,45 +10972,49 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E224" s="4" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12149,45 +12161,49 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E251" s="4" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I251" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>19/31</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13334,45 +13350,49 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B278" s="2" t="inlineStr">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E278" s="4" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I278" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F278" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>26/32</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14515,45 +14535,49 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D305" s="2" t="inlineStr">
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E305" s="2" t="inlineStr">
+      <c r="E305" s="4" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F305" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G305" s="2" t="inlineStr"/>
-      <c r="H305" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I305" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G305" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H305" s="4" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+      <c r="I305" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>7</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         <v>7</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
         <v>7</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>7</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         <v>7</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         <v>6</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8641,45 +8641,45 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G171" s="6" t="inlineStr"/>
-      <c r="H171" s="6" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9830,45 +9830,45 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G198" s="6" t="inlineStr"/>
-      <c r="H198" s="6" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I198" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11019,45 +11019,45 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C225" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D225" s="6" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G225" s="6" t="inlineStr"/>
-      <c r="H225" s="6" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I225" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12208,45 +12208,45 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B252" s="6" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C252" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D252" s="6" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F252" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G252" s="6" t="inlineStr"/>
-      <c r="H252" s="6" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I252" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13397,45 +13397,45 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B279" s="6" t="inlineStr">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C279" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D279" s="6" t="inlineStr">
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F279" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G279" s="6" t="inlineStr"/>
-      <c r="H279" s="6" t="inlineStr">
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I279" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14582,45 +14582,45 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B306" s="6" t="inlineStr">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C306" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D306" s="6" t="inlineStr">
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="E306" s="2" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F306" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G306" s="6" t="inlineStr"/>
-      <c r="H306" s="6" t="inlineStr">
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr"/>
+      <c r="H306" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I306" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -1864,22 +1864,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -1942,22 +1942,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -2020,22 +2020,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -2098,22 +2098,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -2176,22 +2176,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>19</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -8641,45 +8641,49 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E171" s="4" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9830,45 +9834,49 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E198" s="4" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>14/32</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11019,45 +11027,49 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E225" s="4" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12208,45 +12220,49 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E252" s="4" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I252" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13397,45 +13413,49 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B279" s="2" t="inlineStr">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E279" s="4" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I279" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>25/32</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14582,45 +14602,49 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B306" s="2" t="inlineStr">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D306" s="2" t="inlineStr">
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E306" s="2" t="inlineStr">
+      <c r="E306" s="4" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F306" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G306" s="2" t="inlineStr"/>
-      <c r="H306" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I306" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I306" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>8</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         <v>8</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
         <v>8</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         <v>8</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         <v>8</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         <v>7</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8688,45 +8688,45 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr"/>
-      <c r="H172" s="6" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I172" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9881,45 +9881,45 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B199" s="6" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G199" s="6" t="inlineStr"/>
-      <c r="H199" s="6" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I199" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11074,45 +11074,45 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C226" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D226" s="6" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G226" s="6" t="inlineStr"/>
-      <c r="H226" s="6" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I226" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12267,45 +12267,45 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B253" s="6" t="inlineStr">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C253" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D253" s="6" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F253" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G253" s="6" t="inlineStr"/>
-      <c r="H253" s="6" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I253" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13460,45 +13460,45 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B280" s="6" t="inlineStr">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C280" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D280" s="6" t="inlineStr">
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F280" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G280" s="6" t="inlineStr"/>
-      <c r="H280" s="6" t="inlineStr">
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I280" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14649,45 +14649,45 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B307" s="6" t="inlineStr">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D307" s="6" t="inlineStr">
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="E307" s="2" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F307" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G307" s="6" t="inlineStr"/>
-      <c r="H307" s="6" t="inlineStr">
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I307" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -1864,22 +1864,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>
@@ -1942,22 +1942,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -2020,22 +2020,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
     </row>
@@ -2098,22 +2098,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -2176,22 +2176,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>72.8%</t>
         </is>
       </c>
     </row>
@@ -8688,45 +8688,49 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E172" s="4" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9881,45 +9885,49 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="4" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>13/32</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11074,45 +11082,49 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E226" s="4" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I226" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12267,45 +12279,49 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E253" s="4" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I253" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13460,45 +13476,49 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B280" s="2" t="inlineStr">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E280" s="4" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I280" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>21/32</t>
+        </is>
+      </c>
+      <c r="I280" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14649,45 +14669,49 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B307" s="2" t="inlineStr">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D307" s="2" t="inlineStr">
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E307" s="2" t="inlineStr">
+      <c r="E307" s="4" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F307" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G307" s="2" t="inlineStr"/>
-      <c r="H307" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I307" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H307" s="4" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+      <c r="I307" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -1038,45 +1038,45 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1321,10 +1321,10 @@
         <v>8</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         <v>8</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>8</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         <v>8</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         <v>8</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1711,10 +1711,10 @@
         <v>8</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2766,45 +2766,45 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3959,45 +3959,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr"/>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5152,45 +5152,45 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6345,45 +6345,45 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7538,45 +7538,45 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
     </row>
@@ -1033,50 +1033,54 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -1318,22 +1322,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1400,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -1474,22 +1478,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -1552,22 +1556,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -1630,22 +1634,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -1708,22 +1712,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -2766,45 +2770,49 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3959,45 +3967,49 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>17/31</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5152,45 +5164,49 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6345,45 +6361,49 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>17/31</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7538,45 +7558,49 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9">
@@ -1085,45 +1085,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -1325,10 +1325,10 @@
         <v>9</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
         <v>9</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         <v>9</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>9</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         <v>9</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         <v>9</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2817,45 +2817,45 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4014,45 +4014,45 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5211,45 +5211,45 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6408,45 +6408,45 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7605,45 +7605,45 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F147" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G147" s="6" t="inlineStr"/>
-      <c r="H147" s="6" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
@@ -1128,45 +1128,45 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1325,10 +1325,10 @@
         <v>9</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
         <v>9</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
         <v>9</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>9</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         <v>9</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         <v>9</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2860,45 +2860,45 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4057,45 +4057,45 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr"/>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5254,45 +5254,45 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6451,45 +6451,45 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr"/>
-      <c r="H121" s="6" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7648,45 +7648,45 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="6" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
     </row>
@@ -1085,45 +1085,49 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -1322,22 +1326,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>15</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.1%</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1404,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>15</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -1478,22 +1482,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>15</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1560,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>15</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -1634,22 +1638,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>15</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -1712,22 +1716,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>15</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -2817,88 +2821,96 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4014,88 +4026,96 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>16/31</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5211,88 +5231,96 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6408,88 +6436,96 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7605,88 +7641,96 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E147" s="4" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9">
@@ -1797,10 +1797,10 @@
         <v>9</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
         <v>9</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         <v>9</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         <v>9</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
         <v>9</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         <v>8</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8803,45 +8803,45 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G173" s="6" t="inlineStr"/>
-      <c r="H173" s="6" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10000,45 +10000,45 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B200" s="6" t="inlineStr">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C200" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G200" s="6" t="inlineStr"/>
-      <c r="H200" s="6" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I200" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11197,45 +11197,45 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B227" s="6" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C227" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D227" s="6" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G227" s="6" t="inlineStr"/>
-      <c r="H227" s="6" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I227" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12394,45 +12394,45 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B254" s="6" t="inlineStr">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C254" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D254" s="6" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F254" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G254" s="6" t="inlineStr"/>
-      <c r="H254" s="6" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I254" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13591,45 +13591,45 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B281" s="6" t="inlineStr">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C281" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D281" s="6" t="inlineStr">
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="E281" s="2" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F281" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G281" s="6" t="inlineStr"/>
-      <c r="H281" s="6" t="inlineStr">
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I281" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14784,45 +14784,45 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B308" s="6" t="inlineStr">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C308" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D308" s="6" t="inlineStr">
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="E308" s="2" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F308" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G308" s="6" t="inlineStr"/>
-      <c r="H308" s="6" t="inlineStr">
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr"/>
+      <c r="H308" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I308" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -1794,22 +1794,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -1872,22 +1872,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -1950,22 +1950,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -2028,22 +2028,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -2106,22 +2106,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -2184,22 +2184,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -8803,45 +8803,49 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="4" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10000,45 +10004,49 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E200" s="4" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>16/32</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11197,45 +11205,49 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E227" s="4" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I227" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12394,45 +12406,49 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E254" s="4" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I254" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13591,45 +13607,49 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B281" s="2" t="inlineStr">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E281" s="4" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G281" s="2" t="inlineStr"/>
-      <c r="H281" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I281" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>21/32</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14784,45 +14804,49 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="inlineStr">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D308" s="2" t="inlineStr">
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E308" s="2" t="inlineStr">
+      <c r="E308" s="4" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F308" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G308" s="2" t="inlineStr"/>
-      <c r="H308" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I308" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G308" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H308" s="4" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I308" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9">
@@ -1797,10 +1797,10 @@
         <v>10</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
         <v>10</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         <v>10</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
         <v>10</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         <v>9</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8850,45 +8850,45 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G174" s="6" t="inlineStr"/>
-      <c r="H174" s="6" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I174" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10051,45 +10051,45 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B201" s="6" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C201" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D201" s="6" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F201" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G201" s="6" t="inlineStr"/>
-      <c r="H201" s="6" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I201" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11252,45 +11252,45 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B228" s="6" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C228" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D228" s="6" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F228" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G228" s="6" t="inlineStr"/>
-      <c r="H228" s="6" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I228" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12453,45 +12453,45 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B255" s="6" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C255" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D255" s="6" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F255" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G255" s="6" t="inlineStr"/>
-      <c r="H255" s="6" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I255" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13654,45 +13654,45 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B282" s="6" t="inlineStr">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C282" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D282" s="6" t="inlineStr">
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F282" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G282" s="6" t="inlineStr"/>
-      <c r="H282" s="6" t="inlineStr">
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I282" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14851,45 +14851,45 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B309" s="6" t="inlineStr">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C309" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D309" s="6" t="inlineStr">
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="2" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F309" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G309" s="6" t="inlineStr"/>
-      <c r="H309" s="6" t="inlineStr">
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr"/>
+      <c r="H309" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I309" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -1132,45 +1132,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>16/03/2026</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>28/29</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1180,45 +1184,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1326,22 +1334,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1427,7 @@
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1794,22 +1802,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>16</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -1872,22 +1880,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>16</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -1950,22 +1958,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>16</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.6%</t>
         </is>
       </c>
     </row>
@@ -2028,22 +2036,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>16</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -2106,22 +2114,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>16</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -2184,22 +2192,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>16</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>72.8%</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2913,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>30/30</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -8850,45 +8858,49 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="4" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10051,45 +10063,49 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E201" s="4" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>10/32</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11252,45 +11268,49 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E228" s="4" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I228" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12453,45 +12473,49 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E255" s="4" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I255" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>15/31</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13654,45 +13678,49 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E282" s="4" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I282" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>18/32</t>
+        </is>
+      </c>
+      <c r="I282" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14851,45 +14879,49 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B309" s="2" t="inlineStr">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D309" s="2" t="inlineStr">
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E309" s="2" t="inlineStr">
+      <c r="E309" s="4" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F309" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G309" s="2" t="inlineStr"/>
-      <c r="H309" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I309" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G309" s="4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H309" s="4" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+      <c r="I309" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
@@ -1805,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         <v>11</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         <v>11</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>11</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         <v>11</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>10</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
@@ -8905,45 +8905,45 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G175" s="6" t="inlineStr"/>
-      <c r="H175" s="6" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I175" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10110,45 +10110,45 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C202" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D202" s="6" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F202" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G202" s="6" t="inlineStr"/>
-      <c r="H202" s="6" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I202" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11315,45 +11315,45 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B229" s="6" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C229" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D229" s="6" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F229" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G229" s="6" t="inlineStr"/>
-      <c r="H229" s="6" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I229" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12520,45 +12520,45 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B256" s="6" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C256" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D256" s="6" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F256" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G256" s="6" t="inlineStr"/>
-      <c r="H256" s="6" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I256" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13725,45 +13725,45 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B283" s="6" t="inlineStr">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C283" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D283" s="6" t="inlineStr">
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F283" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G283" s="6" t="inlineStr"/>
-      <c r="H283" s="6" t="inlineStr">
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I283" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14926,45 +14926,45 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B310" s="6" t="inlineStr">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C310" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D310" s="6" t="inlineStr">
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="E310" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F310" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G310" s="6" t="inlineStr"/>
-      <c r="H310" s="6" t="inlineStr">
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr"/>
+      <c r="H310" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I310" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H275" s="4" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H276" s="4" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H277" s="4" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H278" s="4" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H279" s="4" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H280" s="4" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H281" s="4" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="4" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H299" s="4" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H300" s="4" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H301" s="4" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H304" s="4" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H305" s="4" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H306" s="4" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H307" s="4" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H308" s="4" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H309" s="4" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
@@ -1415,10 +1415,10 @@
         <v>11</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         <v>11</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         <v>11</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         <v>11</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         <v>11</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2923,45 +2923,45 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4128,45 +4128,45 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5333,45 +5333,45 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6538,45 +6538,45 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="6" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7743,45 +7743,45 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G149" s="6" t="inlineStr"/>
-      <c r="H149" s="6" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -976,7 +976,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>25/29</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
     </row>
@@ -1412,22 +1412,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>14</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -1490,22 +1490,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>14</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -1568,22 +1568,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>14</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.9%</t>
         </is>
       </c>
     </row>
@@ -1646,22 +1646,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -1724,22 +1724,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>14</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>60.1%</t>
         </is>
       </c>
     </row>
@@ -2923,45 +2923,49 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4128,45 +4132,49 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>30/31</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5333,45 +5341,49 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6538,45 +6550,49 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" s="4" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>30/31</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7743,45 +7759,49 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E149" s="4" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
@@ -1276,45 +1276,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>29/03/2026</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1337,10 +1337,10 @@
         <v>12</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>12</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         <v>12</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         <v>12</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         <v>12</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         <v>12</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
@@ -2970,45 +2970,45 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>29/03/2026</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4179,45 +4179,45 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>29/03/2026</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5388,45 +5388,45 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>29/03/2026</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6597,45 +6597,45 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>29/03/2026</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7806,45 +7806,45 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>29/03/2026</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="6" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -1654,22 +1654,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -1810,22 +1810,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -1888,22 +1888,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1966,22 +1966,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -2044,22 +2044,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -2122,22 +2122,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>67.2%</t>
         </is>
       </c>
     </row>
@@ -6022,45 +6022,49 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>21/02/2026</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7235,45 +7239,49 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>21/02/2026</t>
         </is>
       </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8965,45 +8973,49 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="9" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C175" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="9" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E175" s="9" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F175" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G175" s="9" t="inlineStr"/>
-      <c r="H175" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I175" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10170,45 +10182,49 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B202" s="9" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C202" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D202" s="9" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E202" s="9" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F202" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G202" s="9" t="inlineStr"/>
-      <c r="H202" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I202" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>32/32</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11375,45 +11391,49 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B229" s="9" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C229" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D229" s="9" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E229" s="9" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F229" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G229" s="9" t="inlineStr"/>
-      <c r="H229" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I229" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12580,45 +12600,49 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B256" s="9" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C256" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D256" s="9" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E256" s="9" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F256" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G256" s="9" t="inlineStr"/>
-      <c r="H256" s="9" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I256" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13785,45 +13809,49 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B283" s="9" t="inlineStr">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C283" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D283" s="9" t="inlineStr">
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E283" s="9" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F283" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G283" s="9" t="inlineStr"/>
-      <c r="H283" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I283" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>32/32</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -2200,22 +2200,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>15</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
@@ -15014,45 +15014,49 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B310" s="9" t="inlineStr">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C310" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D310" s="9" t="inlineStr">
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E310" s="9" t="inlineStr">
+      <c r="E310" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F310" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G310" s="9" t="inlineStr"/>
-      <c r="H310" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I310" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
@@ -1817,10 +1817,10 @@
         <v>12</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
         <v>12</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         <v>12</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         <v>12</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         <v>12</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
         <v>11</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9044,45 +9044,45 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr">
+      <c r="E176" s="9" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr"/>
-      <c r="H176" s="5" t="inlineStr">
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr"/>
+      <c r="H176" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10253,45 +10253,45 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B203" s="5" t="inlineStr">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B203" s="9" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C203" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E203" s="5" t="inlineStr">
+      <c r="E203" s="9" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G203" s="5" t="inlineStr"/>
-      <c r="H203" s="5" t="inlineStr">
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G203" s="9" t="inlineStr"/>
+      <c r="H203" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I203" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I203" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11462,45 +11462,45 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B230" s="5" t="inlineStr">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C230" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D230" s="5" t="inlineStr">
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E230" s="5" t="inlineStr">
+      <c r="E230" s="9" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G230" s="5" t="inlineStr"/>
-      <c r="H230" s="5" t="inlineStr">
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr"/>
+      <c r="H230" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I230" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I230" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12671,45 +12671,45 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B257" s="5" t="inlineStr">
+      <c r="A257" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B257" s="9" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C257" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D257" s="5" t="inlineStr">
+      <c r="C257" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E257" s="5" t="inlineStr">
+      <c r="E257" s="9" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G257" s="5" t="inlineStr"/>
-      <c r="H257" s="5" t="inlineStr">
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G257" s="9" t="inlineStr"/>
+      <c r="H257" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I257" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I257" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13880,45 +13880,45 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B284" s="5" t="inlineStr">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B284" s="9" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C284" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D284" s="5" t="inlineStr">
+      <c r="C284" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E284" s="5" t="inlineStr">
+      <c r="E284" s="9" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F284" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G284" s="5" t="inlineStr"/>
-      <c r="H284" s="5" t="inlineStr">
+      <c r="F284" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G284" s="9" t="inlineStr"/>
+      <c r="H284" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I284" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I284" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15085,45 +15085,45 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B311" s="5" t="inlineStr">
+      <c r="A311" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B311" s="9" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C311" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D311" s="5" t="inlineStr">
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D311" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E311" s="5" t="inlineStr">
+      <c r="E311" s="9" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F311" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G311" s="5" t="inlineStr"/>
-      <c r="H311" s="5" t="inlineStr">
+      <c r="F311" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G311" s="9" t="inlineStr"/>
+      <c r="H311" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I311" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I311" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.5%</t>
         </is>
       </c>
     </row>
@@ -1814,22 +1814,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -1892,22 +1892,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -1970,22 +1970,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.7%</t>
         </is>
       </c>
     </row>
@@ -2048,22 +2048,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -2126,22 +2126,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -2204,22 +2204,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -9044,45 +9044,49 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="9" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C176" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="9" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E176" s="9" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="9" t="inlineStr"/>
-      <c r="H176" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10253,45 +10257,49 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B203" s="9" t="inlineStr">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C203" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D203" s="9" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E203" s="9" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F203" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G203" s="9" t="inlineStr"/>
-      <c r="H203" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I203" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>28/32</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11462,45 +11470,49 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B230" s="9" t="inlineStr">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C230" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D230" s="9" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E230" s="9" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F230" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G230" s="9" t="inlineStr"/>
-      <c r="H230" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I230" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12671,45 +12683,49 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B257" s="9" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C257" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D257" s="9" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E257" s="9" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F257" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G257" s="9" t="inlineStr"/>
-      <c r="H257" s="9" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I257" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>28/31</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13880,45 +13896,49 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B284" s="9" t="inlineStr">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C284" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D284" s="9" t="inlineStr">
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E284" s="9" t="inlineStr">
+      <c r="E284" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F284" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G284" s="9" t="inlineStr"/>
-      <c r="H284" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I284" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>29/32</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15085,45 +15105,49 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B311" s="9" t="inlineStr">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C311" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D311" s="9" t="inlineStr">
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E311" s="9" t="inlineStr">
+      <c r="E311" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F311" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G311" s="9" t="inlineStr"/>
-      <c r="H311" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I311" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -1817,10 +1817,10 @@
         <v>13</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         <v>13</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         <v>13</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         <v>13</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
         <v>12</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9091,45 +9091,45 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E177" s="5" t="inlineStr">
+      <c r="E177" s="9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="5" t="inlineStr"/>
-      <c r="H177" s="5" t="inlineStr">
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="9" t="inlineStr"/>
+      <c r="H177" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10304,45 +10304,45 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B204" s="5" t="inlineStr">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B204" s="9" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D204" s="5" t="inlineStr">
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E204" s="5" t="inlineStr">
+      <c r="E204" s="9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F204" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G204" s="5" t="inlineStr"/>
-      <c r="H204" s="5" t="inlineStr">
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G204" s="9" t="inlineStr"/>
+      <c r="H204" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I204" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I204" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11517,45 +11517,45 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B231" s="5" t="inlineStr">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D231" s="5" t="inlineStr">
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E231" s="5" t="inlineStr">
+      <c r="E231" s="9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr"/>
-      <c r="H231" s="5" t="inlineStr">
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr"/>
+      <c r="H231" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I231" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I231" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12730,45 +12730,45 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B258" s="5" t="inlineStr">
+      <c r="A258" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B258" s="9" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C258" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D258" s="5" t="inlineStr">
+      <c r="C258" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E258" s="5" t="inlineStr">
+      <c r="E258" s="9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F258" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G258" s="5" t="inlineStr"/>
-      <c r="H258" s="5" t="inlineStr">
+      <c r="F258" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G258" s="9" t="inlineStr"/>
+      <c r="H258" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I258" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I258" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13943,45 +13943,45 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B285" s="5" t="inlineStr">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C285" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D285" s="5" t="inlineStr">
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E285" s="5" t="inlineStr">
+      <c r="E285" s="9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G285" s="5" t="inlineStr"/>
-      <c r="H285" s="5" t="inlineStr">
+      <c r="F285" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G285" s="9" t="inlineStr"/>
+      <c r="H285" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I285" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I285" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15152,45 +15152,45 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B312" s="5" t="inlineStr">
+      <c r="A312" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B312" s="9" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C312" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D312" s="5" t="inlineStr">
+      <c r="C312" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D312" s="9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E312" s="5" t="inlineStr">
+      <c r="E312" s="9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F312" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G312" s="5" t="inlineStr"/>
-      <c r="H312" s="5" t="inlineStr">
+      <c r="F312" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G312" s="9" t="inlineStr"/>
+      <c r="H312" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I312" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I312" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
@@ -850,7 +850,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -905,7 +905,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1814,22 +1814,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -1892,22 +1892,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -1970,22 +1970,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.5%</t>
         </is>
       </c>
     </row>
@@ -2048,22 +2048,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -2126,22 +2126,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -2204,22 +2204,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>13</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9091,45 +9091,49 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="9" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr"/>
-      <c r="H177" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I177" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9729,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9772,7 +9776,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9819,7 +9823,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9866,7 +9870,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9913,7 +9917,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9960,7 +9964,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10007,7 +10011,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10054,7 +10058,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10101,7 +10105,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10148,7 +10152,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10195,7 +10199,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10242,7 +10246,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10289,7 +10293,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10304,45 +10308,49 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B204" s="9" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C204" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D204" s="9" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E204" s="9" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F204" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G204" s="9" t="inlineStr"/>
-      <c r="H204" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I204" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>28/32</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10946,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -10985,7 +10993,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11032,7 +11040,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11079,7 +11087,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11126,7 +11134,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11173,7 +11181,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11220,7 +11228,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11267,7 +11275,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11314,7 +11322,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11361,7 +11369,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11408,7 +11416,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11455,7 +11463,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11502,7 +11510,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11517,45 +11525,49 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B231" s="9" t="inlineStr">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C231" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D231" s="9" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E231" s="9" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F231" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G231" s="9" t="inlineStr"/>
-      <c r="H231" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I231" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12163,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12198,7 +12210,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12245,7 +12257,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12292,7 +12304,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12339,7 +12351,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12386,7 +12398,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12433,7 +12445,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12480,7 +12492,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12527,7 +12539,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12574,7 +12586,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12621,7 +12633,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12668,7 +12680,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12715,7 +12727,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12730,45 +12742,49 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B258" s="9" t="inlineStr">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C258" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D258" s="9" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E258" s="9" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F258" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G258" s="9" t="inlineStr"/>
-      <c r="H258" s="9" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I258" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13380,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13411,7 +13427,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13458,7 +13474,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13505,7 +13521,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13552,7 +13568,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13599,7 +13615,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13646,7 +13662,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -13693,7 +13709,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13740,7 +13756,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13787,7 +13803,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13834,7 +13850,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13881,7 +13897,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13928,7 +13944,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13943,45 +13959,49 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B285" s="9" t="inlineStr">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C285" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D285" s="9" t="inlineStr">
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E285" s="9" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F285" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G285" s="9" t="inlineStr"/>
-      <c r="H285" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I285" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>28/32</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14577,7 +14597,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14624,7 +14644,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14671,7 +14691,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14718,7 +14738,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14808,7 +14828,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -14855,7 +14875,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -14902,7 +14922,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -14949,7 +14969,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14996,7 +15016,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15043,7 +15063,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15090,7 +15110,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15137,7 +15157,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15152,45 +15172,49 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B312" s="9" t="inlineStr">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C312" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D312" s="9" t="inlineStr">
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E312" s="9" t="inlineStr">
+      <c r="E312" s="2" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F312" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G312" s="9" t="inlineStr"/>
-      <c r="H312" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I312" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9">
@@ -1817,10 +1817,10 @@
         <v>14</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
         <v>14</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         <v>14</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         <v>14</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         <v>14</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
         <v>13</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9138,45 +9138,45 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="5" t="inlineStr">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C178" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E178" s="5" t="inlineStr">
+      <c r="E178" s="9" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr"/>
-      <c r="H178" s="5" t="inlineStr">
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr"/>
+      <c r="H178" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I178" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10355,45 +10355,45 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B205" s="5" t="inlineStr">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B205" s="9" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C205" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D205" s="5" t="inlineStr">
+      <c r="C205" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E205" s="5" t="inlineStr">
+      <c r="E205" s="9" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr"/>
-      <c r="H205" s="5" t="inlineStr">
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G205" s="9" t="inlineStr"/>
+      <c r="H205" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I205" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I205" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11572,45 +11572,45 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B232" s="5" t="inlineStr">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B232" s="9" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D232" s="5" t="inlineStr">
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E232" s="5" t="inlineStr">
+      <c r="E232" s="9" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G232" s="5" t="inlineStr"/>
-      <c r="H232" s="5" t="inlineStr">
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G232" s="9" t="inlineStr"/>
+      <c r="H232" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I232" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I232" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12789,45 +12789,45 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B259" s="5" t="inlineStr">
+      <c r="A259" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B259" s="9" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C259" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D259" s="5" t="inlineStr">
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E259" s="5" t="inlineStr">
+      <c r="E259" s="9" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F259" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G259" s="5" t="inlineStr"/>
-      <c r="H259" s="5" t="inlineStr">
+      <c r="F259" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G259" s="9" t="inlineStr"/>
+      <c r="H259" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I259" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I259" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14006,45 +14006,45 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B286" s="5" t="inlineStr">
+      <c r="A286" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B286" s="9" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C286" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D286" s="5" t="inlineStr">
+      <c r="C286" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E286" s="5" t="inlineStr">
+      <c r="E286" s="9" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F286" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G286" s="5" t="inlineStr"/>
-      <c r="H286" s="5" t="inlineStr">
+      <c r="F286" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G286" s="9" t="inlineStr"/>
+      <c r="H286" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I286" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I286" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15219,45 +15219,45 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B313" s="5" t="inlineStr">
+      <c r="A313" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B313" s="9" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C313" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D313" s="5" t="inlineStr">
+      <c r="C313" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D313" s="9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E313" s="5" t="inlineStr">
+      <c r="E313" s="9" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F313" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G313" s="5" t="inlineStr"/>
-      <c r="H313" s="5" t="inlineStr">
+      <c r="F313" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G313" s="9" t="inlineStr"/>
+      <c r="H313" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I313" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I313" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -1814,22 +1814,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -1892,22 +1892,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -1970,22 +1970,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -2048,17 +2048,17 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -2126,22 +2126,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -2204,22 +2204,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -9138,45 +9138,49 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="9" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C178" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D178" s="9" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E178" s="9" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G178" s="9" t="inlineStr"/>
-      <c r="H178" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10355,45 +10359,49 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B205" s="9" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C205" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D205" s="9" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E205" s="9" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F205" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G205" s="9" t="inlineStr"/>
-      <c r="H205" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I205" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>24/32</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11572,45 +11580,49 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B232" s="9" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C232" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D232" s="9" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E232" s="9" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F232" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G232" s="9" t="inlineStr"/>
-      <c r="H232" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I232" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12789,45 +12801,49 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B259" s="9" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C259" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D259" s="9" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E259" s="9" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F259" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G259" s="9" t="inlineStr"/>
-      <c r="H259" s="9" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I259" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14006,45 +14022,49 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B286" s="9" t="inlineStr">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C286" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D286" s="9" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E286" s="9" t="inlineStr">
+      <c r="E286" s="2" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F286" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G286" s="9" t="inlineStr"/>
-      <c r="H286" s="9" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I286" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>28/32</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15219,45 +15239,49 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B313" s="9" t="inlineStr">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C313" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D313" s="9" t="inlineStr">
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E313" s="9" t="inlineStr">
+      <c r="E313" s="2" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F313" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G313" s="9" t="inlineStr"/>
-      <c r="H313" s="9" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I313" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>29/31</t>
+          <t>29/29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>16/29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -855,7 +855,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>15/29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -910,7 +910,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>21/29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>16/29</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>21/29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28/31</t>
+          <t>28/29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>25/29</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>17/29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>27</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>21/29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>27</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>27</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>27</v>
@@ -1711,7 +1711,7 @@
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>27</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1808,28 +1808,28 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="P21" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>15</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>27</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="M23" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>27</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>27</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2120,28 +2120,28 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>31/31</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/31</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/31</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/31</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/31</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/31</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>29/30</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -4377,7 +4377,7 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -4420,7 +4420,7 @@
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -4463,7 +4463,7 @@
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -4506,7 +4506,7 @@
       <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -4549,7 +4549,7 @@
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -4592,7 +4592,7 @@
       <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -4635,7 +4635,7 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
@@ -4678,7 +4678,7 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -4721,7 +4721,7 @@
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -4807,7 +4807,7 @@
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>28/28</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/28</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/28</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/28</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/28</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/28</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/28</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/28</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/28</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/28</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/28</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/28</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/28</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>15/28</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/28</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
@@ -5598,7 +5598,7 @@
       <c r="G99" s="5" t="inlineStr"/>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
@@ -5641,7 +5641,7 @@
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
@@ -5684,7 +5684,7 @@
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -5770,7 +5770,7 @@
       <c r="G103" s="5" t="inlineStr"/>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="G104" s="5" t="inlineStr"/>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
@@ -5856,7 +5856,7 @@
       <c r="G105" s="5" t="inlineStr"/>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -5899,7 +5899,7 @@
       <c r="G106" s="5" t="inlineStr"/>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
@@ -5942,7 +5942,7 @@
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -5985,7 +5985,7 @@
       <c r="G108" s="5" t="inlineStr"/>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -6028,7 +6028,7 @@
       <c r="G109" s="5" t="inlineStr"/>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/28</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>31/31</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/31</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/31</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>29/30</t>
+          <t>30/31</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/31</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/31</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -6819,7 +6819,7 @@
       <c r="G126" s="5" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -6862,7 +6862,7 @@
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
@@ -6905,7 +6905,7 @@
       <c r="G128" s="5" t="inlineStr"/>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
@@ -6948,7 +6948,7 @@
       <c r="G129" s="5" t="inlineStr"/>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
@@ -6991,7 +6991,7 @@
       <c r="G130" s="5" t="inlineStr"/>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
@@ -7034,7 +7034,7 @@
       <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
@@ -7077,7 +7077,7 @@
       <c r="G132" s="5" t="inlineStr"/>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
@@ -7120,7 +7120,7 @@
       <c r="G133" s="5" t="inlineStr"/>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -7163,7 +7163,7 @@
       <c r="G134" s="5" t="inlineStr"/>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -7206,7 +7206,7 @@
       <c r="G135" s="5" t="inlineStr"/>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
@@ -7249,7 +7249,7 @@
       <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>29/29</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/29</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>11/29</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/29</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/29</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/29</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/29</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/29</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/29</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/29</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/29</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -7997,7 +7997,7 @@
       <c r="G152" s="5" t="inlineStr"/>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
@@ -8040,7 +8040,7 @@
       <c r="G153" s="5" t="inlineStr"/>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
@@ -8083,7 +8083,7 @@
       <c r="G154" s="5" t="inlineStr"/>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -8126,7 +8126,7 @@
       <c r="G155" s="5" t="inlineStr"/>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I155" s="5" t="inlineStr">
@@ -8169,7 +8169,7 @@
       <c r="G156" s="5" t="inlineStr"/>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       <c r="G157" s="5" t="inlineStr"/>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
@@ -8255,7 +8255,7 @@
       <c r="G158" s="5" t="inlineStr"/>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
@@ -8298,7 +8298,7 @@
       <c r="G159" s="5" t="inlineStr"/>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
@@ -8341,7 +8341,7 @@
       <c r="G160" s="5" t="inlineStr"/>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
@@ -8384,7 +8384,7 @@
       <c r="G161" s="5" t="inlineStr"/>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I161" s="5" t="inlineStr">
@@ -8427,7 +8427,7 @@
       <c r="G162" s="5" t="inlineStr"/>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I162" s="5" t="inlineStr">
@@ -8470,7 +8470,7 @@
       <c r="G163" s="5" t="inlineStr"/>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I163" s="5" t="inlineStr">
@@ -8480,647 +8480,707 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="9" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C164" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D164" s="9" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E164" s="9" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G164" s="9" t="inlineStr"/>
-      <c r="H164" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I164" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B165" s="9" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C165" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D165" s="9" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E165" s="9" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>25/02/2026</t>
         </is>
       </c>
-      <c r="F165" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G165" s="9" t="inlineStr"/>
-      <c r="H165" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B166" s="9" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C166" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D166" s="9" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E166" s="9" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G166" s="9" t="inlineStr"/>
-      <c r="H166" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B167" s="9" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C167" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E167" s="9" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G167" s="9" t="inlineStr"/>
-      <c r="H167" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I167" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="9" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C168" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D168" s="9" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E168" s="9" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F168" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G168" s="9" t="inlineStr"/>
-      <c r="H168" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I168" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I169" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B170" s="9" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C170" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D170" s="9" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E170" s="9" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="F170" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G170" s="9" t="inlineStr"/>
-      <c r="H170" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I170" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B171" s="9" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C171" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E171" s="9" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>11/03/2026</t>
         </is>
       </c>
-      <c r="F171" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr"/>
-      <c r="H171" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="9" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D172" s="9" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E172" s="9" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>12/03/2026</t>
         </is>
       </c>
-      <c r="F172" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G172" s="9" t="inlineStr"/>
-      <c r="H172" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="9" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C173" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D173" s="9" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E173" s="9" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="F173" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G173" s="9" t="inlineStr"/>
-      <c r="H173" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I173" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="9" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D174" s="9" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E174" s="9" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="F174" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G174" s="9" t="inlineStr"/>
-      <c r="H174" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I174" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="9" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C175" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D175" s="9" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E175" s="9" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="F175" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G175" s="9" t="inlineStr"/>
-      <c r="H175" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I175" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="9" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C176" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D176" s="9" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E176" s="9" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G176" s="9" t="inlineStr"/>
-      <c r="H176" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="9" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr"/>
-      <c r="H177" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I177" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="9" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C178" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D178" s="9" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E178" s="9" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G178" s="9" t="inlineStr"/>
-      <c r="H178" s="9" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9218,7 @@
       <c r="G179" s="5" t="inlineStr"/>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
@@ -9201,7 +9261,7 @@
       <c r="G180" s="5" t="inlineStr"/>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
@@ -9244,7 +9304,7 @@
       <c r="G181" s="5" t="inlineStr"/>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
@@ -9287,7 +9347,7 @@
       <c r="G182" s="5" t="inlineStr"/>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
@@ -9330,7 +9390,7 @@
       <c r="G183" s="5" t="inlineStr"/>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
@@ -9373,7 +9433,7 @@
       <c r="G184" s="5" t="inlineStr"/>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
@@ -9416,7 +9476,7 @@
       <c r="G185" s="5" t="inlineStr"/>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
@@ -9459,7 +9519,7 @@
       <c r="G186" s="5" t="inlineStr"/>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
@@ -9502,7 +9562,7 @@
       <c r="G187" s="5" t="inlineStr"/>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
@@ -9545,7 +9605,7 @@
       <c r="G188" s="5" t="inlineStr"/>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
@@ -9588,7 +9648,7 @@
       <c r="G189" s="5" t="inlineStr"/>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
@@ -9631,7 +9691,7 @@
       <c r="G190" s="5" t="inlineStr"/>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I190" s="5" t="inlineStr">
@@ -9678,7 +9738,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/32</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -9725,7 +9785,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/32</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -9772,7 +9832,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/32</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -9819,7 +9879,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/32</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -9866,7 +9926,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>11/32</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -9913,7 +9973,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/32</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -9960,7 +10020,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/32</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -10007,7 +10067,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/32</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -10054,7 +10114,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/32</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -10101,7 +10161,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>16/32</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -10148,7 +10208,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/32</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -10195,7 +10255,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>29/30</t>
+          <t>32/32</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -10242,7 +10302,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>28/32</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
@@ -10289,7 +10349,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>28/32</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
@@ -10336,7 +10396,7 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/32</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
@@ -10379,7 +10439,7 @@
       <c r="G206" s="5" t="inlineStr"/>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I206" s="5" t="inlineStr">
@@ -10422,7 +10482,7 @@
       <c r="G207" s="5" t="inlineStr"/>
       <c r="H207" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I207" s="5" t="inlineStr">
@@ -10465,7 +10525,7 @@
       <c r="G208" s="5" t="inlineStr"/>
       <c r="H208" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I208" s="5" t="inlineStr">
@@ -10508,7 +10568,7 @@
       <c r="G209" s="5" t="inlineStr"/>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I209" s="5" t="inlineStr">
@@ -10551,7 +10611,7 @@
       <c r="G210" s="5" t="inlineStr"/>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I210" s="5" t="inlineStr">
@@ -10594,7 +10654,7 @@
       <c r="G211" s="5" t="inlineStr"/>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I211" s="5" t="inlineStr">
@@ -10637,7 +10697,7 @@
       <c r="G212" s="5" t="inlineStr"/>
       <c r="H212" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I212" s="5" t="inlineStr">
@@ -10680,7 +10740,7 @@
       <c r="G213" s="5" t="inlineStr"/>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
@@ -10723,7 +10783,7 @@
       <c r="G214" s="5" t="inlineStr"/>
       <c r="H214" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I214" s="5" t="inlineStr">
@@ -10766,7 +10826,7 @@
       <c r="G215" s="5" t="inlineStr"/>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I215" s="5" t="inlineStr">
@@ -10809,7 +10869,7 @@
       <c r="G216" s="5" t="inlineStr"/>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I216" s="5" t="inlineStr">
@@ -10852,7 +10912,7 @@
       <c r="G217" s="5" t="inlineStr"/>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I217" s="5" t="inlineStr">
@@ -10899,7 +10959,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/29</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -10946,7 +11006,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/29</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
@@ -10993,7 +11053,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
@@ -11040,7 +11100,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/29</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
@@ -11087,7 +11147,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
@@ -11134,7 +11194,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
@@ -11181,7 +11241,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/29</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
@@ -11228,7 +11288,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
@@ -11275,7 +11335,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/29</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
@@ -11322,7 +11382,7 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/29</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
@@ -11369,7 +11429,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/29</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
@@ -11416,7 +11476,7 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>29/30</t>
+          <t>29/29</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
@@ -11463,7 +11523,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/29</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
@@ -11510,7 +11570,7 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/29</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -11557,7 +11617,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/29</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
@@ -11600,7 +11660,7 @@
       <c r="G233" s="5" t="inlineStr"/>
       <c r="H233" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I233" s="5" t="inlineStr">
@@ -11643,7 +11703,7 @@
       <c r="G234" s="5" t="inlineStr"/>
       <c r="H234" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I234" s="5" t="inlineStr">
@@ -11686,7 +11746,7 @@
       <c r="G235" s="5" t="inlineStr"/>
       <c r="H235" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I235" s="5" t="inlineStr">
@@ -11729,7 +11789,7 @@
       <c r="G236" s="5" t="inlineStr"/>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I236" s="5" t="inlineStr">
@@ -11772,7 +11832,7 @@
       <c r="G237" s="5" t="inlineStr"/>
       <c r="H237" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I237" s="5" t="inlineStr">
@@ -11815,7 +11875,7 @@
       <c r="G238" s="5" t="inlineStr"/>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I238" s="5" t="inlineStr">
@@ -11858,7 +11918,7 @@
       <c r="G239" s="5" t="inlineStr"/>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I239" s="5" t="inlineStr">
@@ -11901,7 +11961,7 @@
       <c r="G240" s="5" t="inlineStr"/>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
@@ -11944,7 +12004,7 @@
       <c r="G241" s="5" t="inlineStr"/>
       <c r="H241" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I241" s="5" t="inlineStr">
@@ -11987,7 +12047,7 @@
       <c r="G242" s="5" t="inlineStr"/>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I242" s="5" t="inlineStr">
@@ -12030,7 +12090,7 @@
       <c r="G243" s="5" t="inlineStr"/>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I243" s="5" t="inlineStr">
@@ -12073,7 +12133,7 @@
       <c r="G244" s="5" t="inlineStr"/>
       <c r="H244" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/29</t>
         </is>
       </c>
       <c r="I244" s="5" t="inlineStr">
@@ -12120,7 +12180,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
@@ -12167,7 +12227,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
@@ -12214,7 +12274,7 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
@@ -12261,7 +12321,7 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/31</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
@@ -12308,7 +12368,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/31</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
@@ -12355,7 +12415,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
@@ -12402,7 +12462,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
@@ -12449,7 +12509,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/31</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
@@ -12496,7 +12556,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
@@ -12543,7 +12603,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
@@ -12590,7 +12650,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>15/31</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
@@ -12637,7 +12697,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>31/31</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
@@ -12684,7 +12744,7 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/31</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
@@ -12731,7 +12791,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/31</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
@@ -12778,7 +12838,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
@@ -12821,7 +12881,7 @@
       <c r="G260" s="5" t="inlineStr"/>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
@@ -12864,7 +12924,7 @@
       <c r="G261" s="5" t="inlineStr"/>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I261" s="5" t="inlineStr">
@@ -12907,7 +12967,7 @@
       <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I262" s="5" t="inlineStr">
@@ -12950,7 +13010,7 @@
       <c r="G263" s="5" t="inlineStr"/>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I263" s="5" t="inlineStr">
@@ -12993,7 +13053,7 @@
       <c r="G264" s="5" t="inlineStr"/>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I264" s="5" t="inlineStr">
@@ -13036,7 +13096,7 @@
       <c r="G265" s="5" t="inlineStr"/>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I265" s="5" t="inlineStr">
@@ -13079,7 +13139,7 @@
       <c r="G266" s="5" t="inlineStr"/>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I266" s="5" t="inlineStr">
@@ -13122,7 +13182,7 @@
       <c r="G267" s="5" t="inlineStr"/>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I267" s="5" t="inlineStr">
@@ -13165,7 +13225,7 @@
       <c r="G268" s="5" t="inlineStr"/>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I268" s="5" t="inlineStr">
@@ -13208,7 +13268,7 @@
       <c r="G269" s="5" t="inlineStr"/>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I269" s="5" t="inlineStr">
@@ -13251,7 +13311,7 @@
       <c r="G270" s="5" t="inlineStr"/>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I270" s="5" t="inlineStr">
@@ -13294,7 +13354,7 @@
       <c r="G271" s="5" t="inlineStr"/>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/31</t>
         </is>
       </c>
       <c r="I271" s="5" t="inlineStr">
@@ -13341,7 +13401,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/32</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -13388,7 +13448,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/32</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
@@ -13435,7 +13495,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/32</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
@@ -13482,7 +13542,7 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/32</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
@@ -13492,45 +13552,49 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B276" s="9" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C276" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D276" s="9" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E276" s="9" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F276" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G276" s="9" t="inlineStr"/>
-      <c r="H276" s="9" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I276" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>1/32</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13636,7 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/32</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
@@ -13619,7 +13683,7 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/32</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
@@ -13666,7 +13730,7 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/32</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
@@ -13713,7 +13777,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/32</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
@@ -13760,7 +13824,7 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/32</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
@@ -13807,7 +13871,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/32</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
@@ -13854,7 +13918,7 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>32/32</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
@@ -13901,7 +13965,7 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>29/32</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
@@ -13948,7 +14012,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>28/32</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
@@ -13995,7 +14059,7 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>28/32</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
@@ -14038,7 +14102,7 @@
       <c r="G287" s="5" t="inlineStr"/>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I287" s="5" t="inlineStr">
@@ -14081,7 +14145,7 @@
       <c r="G288" s="5" t="inlineStr"/>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
@@ -14124,7 +14188,7 @@
       <c r="G289" s="5" t="inlineStr"/>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I289" s="5" t="inlineStr">
@@ -14167,7 +14231,7 @@
       <c r="G290" s="5" t="inlineStr"/>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I290" s="5" t="inlineStr">
@@ -14210,7 +14274,7 @@
       <c r="G291" s="5" t="inlineStr"/>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I291" s="5" t="inlineStr">
@@ -14253,7 +14317,7 @@
       <c r="G292" s="5" t="inlineStr"/>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I292" s="5" t="inlineStr">
@@ -14296,7 +14360,7 @@
       <c r="G293" s="5" t="inlineStr"/>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
@@ -14339,7 +14403,7 @@
       <c r="G294" s="5" t="inlineStr"/>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I294" s="5" t="inlineStr">
@@ -14382,7 +14446,7 @@
       <c r="G295" s="5" t="inlineStr"/>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I295" s="5" t="inlineStr">
@@ -14425,7 +14489,7 @@
       <c r="G296" s="5" t="inlineStr"/>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I296" s="5" t="inlineStr">
@@ -14468,7 +14532,7 @@
       <c r="G297" s="5" t="inlineStr"/>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I297" s="5" t="inlineStr">
@@ -14511,7 +14575,7 @@
       <c r="G298" s="5" t="inlineStr"/>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>0/30</t>
+          <t>0/32</t>
         </is>
       </c>
       <c r="I298" s="5" t="inlineStr">
@@ -14699,7 +14763,7 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
@@ -14789,7 +14853,7 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
@@ -14836,7 +14900,7 @@
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
@@ -14930,7 +14994,7 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
@@ -14977,7 +15041,7 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
@@ -15071,7 +15135,7 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>29/29</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
@@ -15118,7 +15182,7 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
@@ -15165,7 +15229,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
@@ -15212,7 +15276,7 @@
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>19/32</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>20/32</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>24/32</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>15</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1505,10 +1505,10 @@
         <v>15</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1522,43 +1522,43 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1583,10 +1583,10 @@
         <v>15</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1600,43 +1600,43 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1661,10 +1661,10 @@
         <v>15</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1678,43 +1678,43 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1739,10 +1739,10 @@
         <v>15</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1756,43 +1756,43 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1834,43 +1834,43 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1912,43 +1912,43 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1990,43 +1990,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2068,43 +2068,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2146,43 +2146,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2224,86 +2224,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2474,7 +2474,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2536,7 +2536,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2598,7 +2598,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3118,478 +3118,478 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>A2-A2</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>A2-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4339,478 +4339,478 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>A2-B1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>A2-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5560,478 +5560,478 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>A2-B2</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr"/>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I101" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr"/>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I102" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr"/>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I104" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>A2-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6781,478 +6781,478 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>A2-C1</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I128" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="I129" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="5" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="I130" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="I132" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I133" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>A2-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8002,478 +8002,478 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>A2-C2</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr"/>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr"/>
-      <c r="H153" s="5" t="inlineStr">
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I153" s="5" t="inlineStr">
+      <c r="I154" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr"/>
-      <c r="H154" s="5" t="inlineStr">
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr"/>
+      <c r="H155" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I154" s="5" t="inlineStr">
+      <c r="I155" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="inlineStr"/>
-      <c r="H155" s="5" t="inlineStr">
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I155" s="5" t="inlineStr">
+      <c r="I156" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B156" s="5" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C156" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="inlineStr"/>
-      <c r="H156" s="5" t="inlineStr">
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr"/>
+      <c r="H157" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I156" s="5" t="inlineStr">
+      <c r="I157" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr"/>
-      <c r="H157" s="5" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I157" s="5" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr"/>
-      <c r="H158" s="5" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I158" s="5" t="inlineStr">
+      <c r="I159" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I159" s="5" t="inlineStr">
+      <c r="I160" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I160" s="5" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>A2-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9185,516 +9185,516 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E179" s="5" t="inlineStr">
+      <c r="E179" s="6" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr"/>
-      <c r="H179" s="5" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr"/>
+      <c r="H179" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I179" s="5" t="inlineStr">
+      <c r="I179" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E180" s="5" t="inlineStr">
+      <c r="E180" s="6" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr"/>
-      <c r="H180" s="5" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr"/>
+      <c r="H180" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I180" s="5" t="inlineStr">
+      <c r="I180" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D181" s="5" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E181" s="5" t="inlineStr">
+      <c r="E181" s="6" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G181" s="5" t="inlineStr"/>
-      <c r="H181" s="5" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr"/>
+      <c r="H181" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I181" s="5" t="inlineStr">
+      <c r="I181" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E182" s="5" t="inlineStr">
+      <c r="E182" s="6" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr"/>
+      <c r="H182" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I182" s="5" t="inlineStr">
+      <c r="I182" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="6" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr"/>
+      <c r="H183" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I183" s="5" t="inlineStr">
+      <c r="I183" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
+      <c r="E184" s="6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr"/>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr"/>
+      <c r="H184" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I184" s="5" t="inlineStr">
+      <c r="I184" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="I186" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="I187" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10406,516 +10406,516 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B206" s="5" t="inlineStr">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D206" s="5" t="inlineStr">
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E206" s="5" t="inlineStr">
+      <c r="E206" s="6" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr"/>
-      <c r="H206" s="5" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr"/>
+      <c r="H206" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I206" s="5" t="inlineStr">
+      <c r="I206" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B207" s="5" t="inlineStr">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E207" s="5" t="inlineStr">
+      <c r="E207" s="6" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr"/>
-      <c r="H207" s="5" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr"/>
+      <c r="H207" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I207" s="5" t="inlineStr">
+      <c r="I207" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B208" s="5" t="inlineStr">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D208" s="5" t="inlineStr">
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E208" s="5" t="inlineStr">
+      <c r="E208" s="6" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr"/>
-      <c r="H208" s="5" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr"/>
+      <c r="H208" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I208" s="5" t="inlineStr">
+      <c r="I208" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="inlineStr">
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E209" s="5" t="inlineStr">
+      <c r="E209" s="6" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr"/>
-      <c r="H209" s="5" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr"/>
+      <c r="H209" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I209" s="5" t="inlineStr">
+      <c r="I209" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="6" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr"/>
+      <c r="H210" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I210" s="5" t="inlineStr">
+      <c r="I210" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="5" t="inlineStr">
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E211" s="5" t="inlineStr">
+      <c r="E211" s="6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr"/>
-      <c r="H211" s="5" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr"/>
+      <c r="H211" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I211" s="5" t="inlineStr">
+      <c r="I211" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I212" s="5" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I213" s="5" t="inlineStr">
+      <c r="I213" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="I214" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="I216" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
-      <c r="H217" s="5" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I217" s="5" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11627,516 +11627,516 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="6" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr"/>
-      <c r="H233" s="5" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="6" t="inlineStr"/>
+      <c r="H233" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I233" s="5" t="inlineStr">
+      <c r="I233" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E234" s="5" t="inlineStr">
+      <c r="E234" s="6" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr"/>
-      <c r="H234" s="5" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G234" s="6" t="inlineStr"/>
+      <c r="H234" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I234" s="5" t="inlineStr">
+      <c r="I234" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C235" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D235" s="5" t="inlineStr">
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E235" s="5" t="inlineStr">
+      <c r="E235" s="6" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr"/>
-      <c r="H235" s="5" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G235" s="6" t="inlineStr"/>
+      <c r="H235" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I235" s="5" t="inlineStr">
+      <c r="I235" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E236" s="5" t="inlineStr">
+      <c r="E236" s="6" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="6" t="inlineStr"/>
+      <c r="H236" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I236" s="5" t="inlineStr">
+      <c r="I236" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
+      <c r="E237" s="6" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
-      <c r="H237" s="5" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="6" t="inlineStr"/>
+      <c r="H237" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I237" s="5" t="inlineStr">
+      <c r="I237" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="6" t="inlineStr"/>
+      <c r="H238" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I238" s="5" t="inlineStr">
+      <c r="I238" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr"/>
+      <c r="H239" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="I240" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr"/>
+      <c r="H241" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I241" s="5" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr"/>
+      <c r="H243" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12848,516 +12848,516 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="inlineStr">
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
+      <c r="C260" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D260" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E260" s="5" t="inlineStr">
+      <c r="E260" s="6" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr"/>
-      <c r="H260" s="5" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G260" s="6" t="inlineStr"/>
+      <c r="H260" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I260" s="5" t="inlineStr">
+      <c r="I260" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D261" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E261" s="5" t="inlineStr">
+      <c r="E261" s="6" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr"/>
-      <c r="H261" s="5" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G261" s="6" t="inlineStr"/>
+      <c r="H261" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I261" s="5" t="inlineStr">
+      <c r="I261" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B262" s="5" t="inlineStr">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C262" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D262" s="5" t="inlineStr">
+      <c r="C262" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D262" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E262" s="5" t="inlineStr">
+      <c r="E262" s="6" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F262" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G262" s="5" t="inlineStr"/>
-      <c r="H262" s="5" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G262" s="6" t="inlineStr"/>
+      <c r="H262" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I262" s="5" t="inlineStr">
+      <c r="I262" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C263" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E263" s="5" t="inlineStr">
+      <c r="E263" s="6" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr"/>
-      <c r="H263" s="5" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr"/>
+      <c r="H263" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I263" s="5" t="inlineStr">
+      <c r="I263" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="5" t="inlineStr">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C264" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E264" s="5" t="inlineStr">
+      <c r="E264" s="6" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr"/>
-      <c r="H264" s="5" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr"/>
+      <c r="H264" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I264" s="5" t="inlineStr">
+      <c r="I264" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr"/>
+      <c r="H265" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr"/>
+      <c r="H266" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I266" s="5" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr"/>
+      <c r="H267" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I267" s="5" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr"/>
+      <c r="H268" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
+      <c r="I268" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
-      <c r="H269" s="5" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr"/>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr"/>
+      <c r="H270" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
-      <c r="H271" s="5" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr"/>
+      <c r="H271" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I271" s="5" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14069,516 +14069,516 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
+      <c r="A287" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C287" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D287" s="5" t="inlineStr">
+      <c r="C287" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D287" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E287" s="5" t="inlineStr">
+      <c r="E287" s="6" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F287" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G287" s="5" t="inlineStr"/>
-      <c r="H287" s="5" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G287" s="6" t="inlineStr"/>
+      <c r="H287" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I287" s="5" t="inlineStr">
+      <c r="I287" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="inlineStr">
+      <c r="A288" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C288" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D288" s="5" t="inlineStr">
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D288" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E288" s="5" t="inlineStr">
+      <c r="E288" s="6" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F288" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="5" t="inlineStr"/>
-      <c r="H288" s="5" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="6" t="inlineStr"/>
+      <c r="H288" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I288" s="5" t="inlineStr">
+      <c r="I288" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
+      <c r="A289" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C289" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D289" s="5" t="inlineStr">
+      <c r="C289" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D289" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E289" s="5" t="inlineStr">
+      <c r="E289" s="6" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F289" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G289" s="5" t="inlineStr"/>
-      <c r="H289" s="5" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G289" s="6" t="inlineStr"/>
+      <c r="H289" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I289" s="5" t="inlineStr">
+      <c r="I289" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="5" t="inlineStr">
+      <c r="A290" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C290" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="5" t="inlineStr">
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E290" s="5" t="inlineStr">
+      <c r="E290" s="6" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F290" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="5" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="6" t="inlineStr"/>
+      <c r="H290" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I290" s="5" t="inlineStr">
+      <c r="I290" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="5" t="inlineStr">
+      <c r="A291" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C291" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="5" t="inlineStr">
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E291" s="5" t="inlineStr">
+      <c r="E291" s="6" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="5" t="inlineStr"/>
-      <c r="H291" s="5" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="6" t="inlineStr"/>
+      <c r="H291" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I291" s="5" t="inlineStr">
+      <c r="I291" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C292" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D292" s="5" t="inlineStr">
+      <c r="C292" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D292" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E292" s="5" t="inlineStr">
+      <c r="E292" s="6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F292" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G292" s="5" t="inlineStr"/>
-      <c r="H292" s="5" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G292" s="6" t="inlineStr"/>
+      <c r="H292" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I292" s="5" t="inlineStr">
+      <c r="I292" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr"/>
+      <c r="H293" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
+      <c r="I293" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="5" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="I294" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="5" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr"/>
+      <c r="H295" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
+      <c r="I295" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="5" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr"/>
-      <c r="H297" s="5" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr"/>
+      <c r="H297" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="5" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14773,43 +14773,43 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="9" t="inlineStr">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C303" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="9" t="inlineStr">
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="9" t="inlineStr">
+      <c r="E303" s="5" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F303" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="9" t="inlineStr"/>
-      <c r="H303" s="9" t="inlineStr">
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr"/>
+      <c r="H303" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I303" s="9" t="inlineStr">
+      <c r="I303" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15286,516 +15286,516 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B314" s="5" t="inlineStr">
+      <c r="A314" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C314" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D314" s="5" t="inlineStr">
+      <c r="C314" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D314" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E314" s="5" t="inlineStr">
+      <c r="E314" s="6" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F314" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G314" s="5" t="inlineStr"/>
-      <c r="H314" s="5" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G314" s="6" t="inlineStr"/>
+      <c r="H314" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I314" s="5" t="inlineStr">
+      <c r="I314" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B315" s="5" t="inlineStr">
+      <c r="A315" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B315" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C315" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D315" s="5" t="inlineStr">
+      <c r="C315" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D315" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E315" s="5" t="inlineStr">
+      <c r="E315" s="6" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G315" s="5" t="inlineStr"/>
-      <c r="H315" s="5" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G315" s="6" t="inlineStr"/>
+      <c r="H315" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I315" s="5" t="inlineStr">
+      <c r="I315" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B316" s="5" t="inlineStr">
+      <c r="A316" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B316" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C316" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D316" s="5" t="inlineStr">
+      <c r="C316" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D316" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E316" s="5" t="inlineStr">
+      <c r="E316" s="6" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G316" s="5" t="inlineStr"/>
-      <c r="H316" s="5" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G316" s="6" t="inlineStr"/>
+      <c r="H316" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I316" s="5" t="inlineStr">
+      <c r="I316" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="6" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="6" t="inlineStr"/>
+      <c r="H317" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I317" s="5" t="inlineStr">
+      <c r="I317" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="5" t="inlineStr">
+      <c r="A318" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C318" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="C318" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E318" s="5" t="inlineStr">
+      <c r="E318" s="6" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr"/>
-      <c r="H318" s="5" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="6" t="inlineStr"/>
+      <c r="H318" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I318" s="5" t="inlineStr">
+      <c r="I318" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B319" s="5" t="inlineStr">
+      <c r="A319" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C319" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D319" s="5" t="inlineStr">
+      <c r="C319" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D319" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E319" s="5" t="inlineStr">
+      <c r="E319" s="6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F319" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G319" s="5" t="inlineStr"/>
-      <c r="H319" s="5" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G319" s="6" t="inlineStr"/>
+      <c r="H319" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I319" s="5" t="inlineStr">
+      <c r="I319" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="6" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="I320" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C321" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="C321" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="6" t="inlineStr"/>
+      <c r="H321" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I321" s="5" t="inlineStr">
+      <c r="I321" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="5" t="inlineStr">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C322" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E322" s="5" t="inlineStr">
+      <c r="E322" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr"/>
-      <c r="H322" s="5" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="6" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I322" s="5" t="inlineStr">
+      <c r="I322" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E323" s="5" t="inlineStr">
+      <c r="E323" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr"/>
-      <c r="H323" s="5" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="6" t="inlineStr"/>
+      <c r="H323" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I323" s="5" t="inlineStr">
+      <c r="I323" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E324" s="5" t="inlineStr">
+      <c r="E324" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr"/>
-      <c r="H324" s="5" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E325" s="5" t="inlineStr">
+      <c r="E325" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr"/>
-      <c r="H325" s="5" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="inlineStr"/>
+      <c r="H325" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>15</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>15</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1522,45 +1522,45 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1583,10 +1583,10 @@
         <v>15</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         <v>15</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>15</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -3123,45 +3123,45 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr"/>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4344,45 +4344,45 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5565,45 +5565,45 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6786,45 +6786,45 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="5" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8007,45 +8007,45 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="5" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G153" s="6" t="inlineStr"/>
-      <c r="H153" s="6" t="inlineStr">
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr"/>
+      <c r="H153" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>15</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>15</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>15</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1600,45 +1600,45 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1661,10 +1661,10 @@
         <v>15</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>15</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -3166,45 +3166,45 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4387,45 +4387,45 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr"/>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5608,45 +5608,45 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6829,45 +6829,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8050,45 +8050,45 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="5" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr">
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr"/>
+      <c r="H154" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -1580,65 +1580,69 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1658,22 +1662,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.8%</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1740,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
     </row>
@@ -3166,45 +3170,49 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>29/30</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4387,45 +4395,49 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5608,45 +5620,49 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr"/>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6829,45 +6845,49 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8050,45 +8070,49 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E154" s="5" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr"/>
-      <c r="H154" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I154" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Session Analysis Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session Analysis Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session Analysis Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Session Analysis Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -1821,10 +1821,10 @@
         <v>15</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         <v>15</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1977,10 +1977,10 @@
         <v>15</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
         <v>15</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2133,10 +2133,10 @@
         <v>15</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2211,10 +2211,10 @@
         <v>14</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9209,45 +9209,45 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr"/>
-      <c r="H179" s="6" t="inlineStr">
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr"/>
+      <c r="H179" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I179" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10430,45 +10430,45 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B206" s="6" t="inlineStr">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C206" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G206" s="6" t="inlineStr"/>
-      <c r="H206" s="6" t="inlineStr">
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr"/>
+      <c r="H206" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I206" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I206" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11651,45 +11651,45 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C233" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="6" t="inlineStr">
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E233" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F233" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="6" t="inlineStr"/>
-      <c r="H233" s="6" t="inlineStr">
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr"/>
+      <c r="H233" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I233" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12872,45 +12872,45 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B260" s="6" t="inlineStr">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C260" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D260" s="6" t="inlineStr">
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="E260" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F260" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G260" s="6" t="inlineStr"/>
-      <c r="H260" s="6" t="inlineStr">
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G260" s="5" t="inlineStr"/>
+      <c r="H260" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I260" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I260" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14093,45 +14093,45 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B287" s="6" t="inlineStr">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C287" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D287" s="6" t="inlineStr">
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="E287" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F287" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G287" s="6" t="inlineStr"/>
-      <c r="H287" s="6" t="inlineStr">
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="inlineStr"/>
+      <c r="H287" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I287" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I287" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15310,45 +15310,45 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B314" s="6" t="inlineStr">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C314" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D314" s="6" t="inlineStr">
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="E314" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F314" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G314" s="6" t="inlineStr"/>
-      <c r="H314" s="6" t="inlineStr">
+      <c r="F314" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G314" s="5" t="inlineStr"/>
+      <c r="H314" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I314" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I314" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1818,22 +1818,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1896,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -1974,22 +1974,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -2052,22 +2052,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -2208,22 +2208,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>11</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -9209,45 +9209,49 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E179" s="5" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G179" s="5" t="inlineStr"/>
-      <c r="H179" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10430,45 +10434,49 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B206" s="5" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D206" s="5" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E206" s="5" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G206" s="5" t="inlineStr"/>
-      <c r="H206" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I206" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>29/32</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10991,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -11651,45 +11659,49 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr"/>
-      <c r="H233" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12872,45 +12884,49 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B260" s="5" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E260" s="5" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G260" s="5" t="inlineStr"/>
-      <c r="H260" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I260" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>29/31</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14093,45 +14109,49 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B287" s="5" t="inlineStr">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C287" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D287" s="5" t="inlineStr">
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E287" s="5" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F287" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G287" s="5" t="inlineStr"/>
-      <c r="H287" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I287" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>27/32</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15310,45 +15330,49 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B314" s="5" t="inlineStr">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C314" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D314" s="5" t="inlineStr">
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E314" s="5" t="inlineStr">
+      <c r="E314" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F314" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G314" s="5" t="inlineStr"/>
-      <c r="H314" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I314" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -1502,65 +1502,69 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1580,22 +1584,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -1662,22 +1666,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -1740,22 +1744,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -3127,45 +3131,49 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4352,45 +4360,49 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5577,45 +5589,49 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>28/28</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6802,45 +6818,49 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8027,45 +8047,49 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E153" s="5" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr"/>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
@@ -1825,10 +1825,10 @@
         <v>16</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>16</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         <v>16</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         <v>16</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         <v>16</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         <v>15</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9280,45 +9280,45 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G180" s="6" t="inlineStr"/>
-      <c r="H180" s="6" t="inlineStr">
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr"/>
+      <c r="H180" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I180" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10505,45 +10505,45 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B207" s="6" t="inlineStr">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C207" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D207" s="6" t="inlineStr">
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F207" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G207" s="6" t="inlineStr"/>
-      <c r="H207" s="6" t="inlineStr">
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr"/>
+      <c r="H207" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I207" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11730,45 +11730,45 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B234" s="6" t="inlineStr">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C234" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D234" s="6" t="inlineStr">
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="E234" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F234" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G234" s="6" t="inlineStr"/>
-      <c r="H234" s="6" t="inlineStr">
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr"/>
+      <c r="H234" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I234" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I234" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12955,45 +12955,45 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B261" s="6" t="inlineStr">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C261" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D261" s="6" t="inlineStr">
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E261" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F261" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G261" s="6" t="inlineStr"/>
-      <c r="H261" s="6" t="inlineStr">
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr"/>
+      <c r="H261" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I261" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I261" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14180,45 +14180,45 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B288" s="6" t="inlineStr">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C288" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D288" s="6" t="inlineStr">
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="E288" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F288" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="6" t="inlineStr"/>
-      <c r="H288" s="6" t="inlineStr">
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="5" t="inlineStr"/>
+      <c r="H288" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I288" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I288" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15401,45 +15401,45 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B315" s="6" t="inlineStr">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C315" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D315" s="6" t="inlineStr">
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="E315" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F315" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G315" s="6" t="inlineStr"/>
-      <c r="H315" s="6" t="inlineStr">
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="inlineStr"/>
+      <c r="H315" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I315" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I315" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -1822,22 +1822,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>10</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -1900,22 +1900,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>10</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -1978,22 +1978,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>74.2%</t>
         </is>
       </c>
     </row>
@@ -2134,22 +2134,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>10</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -2212,22 +2212,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>10</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -9280,45 +9280,49 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E180" s="5" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr"/>
-      <c r="H180" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I180" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10505,45 +10509,49 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B207" s="5" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D207" s="5" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E207" s="5" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F207" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G207" s="5" t="inlineStr"/>
-      <c r="H207" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I207" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>24/32</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11730,45 +11738,49 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E234" s="5" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr"/>
-      <c r="H234" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I234" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12955,45 +12967,49 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E261" s="5" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G261" s="5" t="inlineStr"/>
-      <c r="H261" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I261" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>29/31</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14180,45 +14196,49 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B288" s="5" t="inlineStr">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C288" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D288" s="5" t="inlineStr">
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E288" s="5" t="inlineStr">
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F288" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G288" s="5" t="inlineStr"/>
-      <c r="H288" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I288" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>28/32</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15401,45 +15421,49 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B315" s="5" t="inlineStr">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C315" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D315" s="5" t="inlineStr">
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E315" s="5" t="inlineStr">
+      <c r="E315" s="2" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F315" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G315" s="5" t="inlineStr"/>
-      <c r="H315" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I315" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9">
@@ -1825,10 +1825,10 @@
         <v>17</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>17</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         <v>17</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         <v>17</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         <v>17</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         <v>16</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9327,45 +9327,45 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="5" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G181" s="6" t="inlineStr"/>
-      <c r="H181" s="6" t="inlineStr">
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr"/>
+      <c r="H181" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10556,45 +10556,45 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C208" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="5" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G208" s="6" t="inlineStr"/>
-      <c r="H208" s="6" t="inlineStr">
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr"/>
+      <c r="H208" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I208" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11785,45 +11785,45 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C235" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D235" s="6" t="inlineStr">
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="E235" s="5" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F235" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G235" s="6" t="inlineStr"/>
-      <c r="H235" s="6" t="inlineStr">
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr"/>
+      <c r="H235" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I235" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13014,45 +13014,45 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B262" s="6" t="inlineStr">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C262" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D262" s="6" t="inlineStr">
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="E262" s="5" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F262" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G262" s="6" t="inlineStr"/>
-      <c r="H262" s="6" t="inlineStr">
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="inlineStr"/>
+      <c r="H262" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I262" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I262" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14243,45 +14243,45 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B289" s="6" t="inlineStr">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C289" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D289" s="6" t="inlineStr">
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="E289" s="5" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F289" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G289" s="6" t="inlineStr"/>
-      <c r="H289" s="6" t="inlineStr">
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr"/>
+      <c r="H289" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I289" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I289" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15468,45 +15468,45 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B316" s="6" t="inlineStr">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C316" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D316" s="6" t="inlineStr">
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="5" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F316" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G316" s="6" t="inlineStr"/>
-      <c r="H316" s="6" t="inlineStr">
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="inlineStr"/>
+      <c r="H316" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I316" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I316" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>17</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>17</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         <v>17</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1686,45 +1686,45 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1747,10 +1747,10 @@
         <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -3225,45 +3225,45 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr"/>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4454,45 +4454,45 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5683,45 +5683,45 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr"/>
-      <c r="H101" s="6" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6912,45 +6912,45 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="5" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8141,45 +8141,45 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="5" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G155" s="6" t="inlineStr"/>
-      <c r="H155" s="6" t="inlineStr">
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr"/>
+      <c r="H155" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>17</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>17</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         <v>17</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
         <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1764,45 +1764,45 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -3268,45 +3268,45 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4497,45 +4497,45 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr"/>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5726,45 +5726,45 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6955,45 +6955,45 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8184,45 +8184,45 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr"/>
-      <c r="H156" s="6" t="inlineStr">
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr"/>
+      <c r="H156" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>17</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>17</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>17</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         <v>17</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
         <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1842,45 +1842,45 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -3311,45 +3311,45 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr"/>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4540,45 +4540,45 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5769,45 +5769,45 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr"/>
-      <c r="H103" s="6" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6998,45 +6998,45 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="5" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F130" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr">
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8227,45 +8227,45 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="5" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G157" s="6" t="inlineStr"/>
-      <c r="H157" s="6" t="inlineStr">
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr"/>
+      <c r="H157" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I157" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1825,10 +1825,10 @@
         <v>17</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>17</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         <v>17</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         <v>17</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         <v>17</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         <v>16</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9370,45 +9370,45 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="6" t="inlineStr"/>
-      <c r="H182" s="6" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr"/>
+      <c r="H182" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10599,45 +10599,45 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C209" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="6" t="inlineStr">
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F209" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="6" t="inlineStr"/>
-      <c r="H209" s="6" t="inlineStr">
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr"/>
+      <c r="H209" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I209" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I209" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11828,45 +11828,45 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="6" t="inlineStr">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C236" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="6" t="inlineStr">
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F236" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="6" t="inlineStr"/>
-      <c r="H236" s="6" t="inlineStr">
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr"/>
+      <c r="H236" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I236" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I236" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13057,45 +13057,45 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="6" t="inlineStr">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C263" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="6" t="inlineStr">
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E263" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F263" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="6" t="inlineStr"/>
-      <c r="H263" s="6" t="inlineStr">
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr"/>
+      <c r="H263" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I263" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I263" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14286,45 +14286,45 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C290" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="6" t="inlineStr">
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="E290" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F290" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="6" t="inlineStr"/>
-      <c r="H290" s="6" t="inlineStr">
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="inlineStr"/>
+      <c r="H290" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I290" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I290" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15511,45 +15511,45 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="6" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C317" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="6" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F317" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="6" t="inlineStr"/>
-      <c r="H317" s="6" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I317" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I317" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -1825,10 +1825,10 @@
         <v>17</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>17</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         <v>17</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         <v>17</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         <v>17</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         <v>16</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9413,45 +9413,45 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="6" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C183" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="6" t="inlineStr"/>
-      <c r="H183" s="6" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr"/>
+      <c r="H183" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I183" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10642,45 +10642,45 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C210" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="6" t="inlineStr">
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="5" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="6" t="inlineStr"/>
-      <c r="H210" s="6" t="inlineStr">
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr"/>
+      <c r="H210" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I210" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I210" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11871,45 +11871,45 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C237" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="6" t="inlineStr">
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="5" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F237" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="6" t="inlineStr"/>
-      <c r="H237" s="6" t="inlineStr">
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr"/>
+      <c r="H237" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I237" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13100,45 +13100,45 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="6" t="inlineStr">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C264" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="6" t="inlineStr">
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="E264" s="5" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F264" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="6" t="inlineStr"/>
-      <c r="H264" s="6" t="inlineStr">
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="5" t="inlineStr"/>
+      <c r="H264" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I264" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I264" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14329,45 +14329,45 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="6" t="inlineStr">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C291" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="6" t="inlineStr">
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="5" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F291" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="6" t="inlineStr"/>
-      <c r="H291" s="6" t="inlineStr">
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr"/>
+      <c r="H291" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I291" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I291" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15554,45 +15554,45 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="6" t="inlineStr">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C318" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="6" t="inlineStr">
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="5" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F318" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="6" t="inlineStr"/>
-      <c r="H318" s="6" t="inlineStr">
+      <c r="F318" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="5" t="inlineStr"/>
+      <c r="H318" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I318" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I318" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -1822,22 +1822,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>58.4%</t>
         </is>
       </c>
     </row>
@@ -1900,22 +1900,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -1978,22 +1978,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -2134,22 +2134,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -2212,22 +2212,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>7</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -9413,45 +9413,49 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E183" s="5" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F183" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G183" s="5" t="inlineStr"/>
-      <c r="H183" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I183" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10642,45 +10646,49 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="inlineStr">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D210" s="5" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E210" s="5" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr"/>
-      <c r="H210" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I210" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>1/32</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11871,45 +11879,49 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C237" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G237" s="5" t="inlineStr"/>
-      <c r="H237" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13100,45 +13112,49 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B264" s="5" t="inlineStr">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C264" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E264" s="5" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G264" s="5" t="inlineStr"/>
-      <c r="H264" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I264" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>25/31</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14329,45 +14345,49 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B291" s="5" t="inlineStr">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C291" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D291" s="5" t="inlineStr">
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E291" s="5" t="inlineStr">
+      <c r="E291" s="2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G291" s="5" t="inlineStr"/>
-      <c r="H291" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I291" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>27/32</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15554,45 +15574,49 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B318" s="5" t="inlineStr">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C318" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E318" s="5" t="inlineStr">
+      <c r="E318" s="2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr"/>
-      <c r="H318" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I318" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -1825,10 +1825,10 @@
         <v>18</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>18</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         <v>18</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         <v>18</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         <v>18</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         <v>17</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -9460,45 +9460,45 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C184" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr"/>
-      <c r="H184" s="6" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr"/>
+      <c r="H184" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10693,45 +10693,45 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="6" t="inlineStr">
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="E211" s="5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G211" s="6" t="inlineStr"/>
-      <c r="H211" s="6" t="inlineStr">
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr"/>
+      <c r="H211" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I211" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11926,45 +11926,45 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="6" t="inlineStr">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C238" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="6" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F238" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="6" t="inlineStr"/>
-      <c r="H238" s="6" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr"/>
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I238" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I238" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13159,45 +13159,45 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="6" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C265" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="6" t="inlineStr">
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F265" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="6" t="inlineStr"/>
-      <c r="H265" s="6" t="inlineStr">
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
+      <c r="H265" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I265" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I265" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14392,45 +14392,45 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B292" s="6" t="inlineStr">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C292" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D292" s="6" t="inlineStr">
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="E292" s="5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F292" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G292" s="6" t="inlineStr"/>
-      <c r="H292" s="6" t="inlineStr">
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G292" s="5" t="inlineStr"/>
+      <c r="H292" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I292" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I292" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15621,45 +15621,45 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B319" s="6" t="inlineStr">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C319" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D319" s="6" t="inlineStr">
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F319" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G319" s="6" t="inlineStr"/>
-      <c r="H319" s="6" t="inlineStr">
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="inlineStr"/>
+      <c r="H319" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I319" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I319" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>73.5%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -1584,22 +1584,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -1666,65 +1666,69 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1764,45 +1768,49 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1822,65 +1830,69 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1900,22 +1912,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -1978,22 +1990,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -2134,22 +2146,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -2212,22 +2224,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -3225,131 +3237,143 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4454,131 +4478,143 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5683,131 +5719,143 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr"/>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>28/28</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>28/28</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr"/>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>28/28</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6912,131 +6960,143 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9460,45 +9520,49 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E184" s="5" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F184" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr"/>
-      <c r="H184" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I184" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10693,45 +10757,49 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D211" s="5" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E211" s="5" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F211" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr"/>
-      <c r="H211" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I211" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>27/32</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11926,45 +11994,49 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="5" t="inlineStr">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C238" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E238" s="5" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G238" s="5" t="inlineStr"/>
-      <c r="H238" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I238" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14392,45 +14464,49 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B292" s="5" t="inlineStr">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C292" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D292" s="5" t="inlineStr">
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E292" s="5" t="inlineStr">
+      <c r="E292" s="2" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F292" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G292" s="5" t="inlineStr"/>
-      <c r="H292" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I292" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>26/32</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15621,45 +15697,49 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B319" s="5" t="inlineStr">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C319" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D319" s="5" t="inlineStr">
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E319" s="5" t="inlineStr">
+      <c r="E319" s="2" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F319" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G319" s="5" t="inlineStr"/>
-      <c r="H319" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I319" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -1424,65 +1424,69 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1502,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>74.8%</t>
         </is>
       </c>
     </row>
@@ -1584,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1748,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -1830,22 +1834,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -1912,63 +1916,63 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1990,63 +1994,63 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2068,63 +2072,63 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2146,63 +2150,63 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2224,106 +2228,106 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2494,7 +2498,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2556,7 +2560,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2618,7 +2622,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3100,45 +3104,49 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3378,258 +3386,258 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4341,45 +4349,49 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4619,258 +4631,258 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5582,45 +5594,49 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr"/>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5860,258 +5876,258 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I104" s="6" t="inlineStr">
+      <c r="I104" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr"/>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="I105" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
+      <c r="I106" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6823,43 +6839,43 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="I125" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -7101,258 +7117,258 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="inlineStr">
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I131" s="6" t="inlineStr">
+      <c r="I131" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8064,43 +8080,43 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="9" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr"/>
-      <c r="H152" s="5" t="inlineStr">
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr"/>
+      <c r="H152" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I152" s="5" t="inlineStr">
+      <c r="I152" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -8201,387 +8217,399 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="inlineStr"/>
-      <c r="H155" s="5" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>A2-C2</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>A2-C2</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>A2-C2</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr"/>
+      <c r="H158" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I155" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B156" s="5" t="inlineStr">
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C156" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="inlineStr"/>
-      <c r="H156" s="5" t="inlineStr">
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I156" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr"/>
-      <c r="H157" s="5" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
+      <c r="H160" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I157" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="F158" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="6" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I158" s="6" t="inlineStr">
+      <c r="I161" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F159" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="6" t="inlineStr"/>
-      <c r="H159" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I159" s="6" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>A2-C2</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>A2-C2</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>A2-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9387,86 +9415,90 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D181" s="5" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E181" s="5" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G181" s="5" t="inlineStr"/>
-      <c r="H181" s="5" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>A2-D1</t>
+        </is>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="inlineStr"/>
+      <c r="H182" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I181" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
-        <is>
-          <t>A2-D1</t>
-        </is>
-      </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E182" s="5" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="inlineStr">
+      <c r="I182" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9567,258 +9599,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr"/>
+      <c r="H185" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10624,86 +10656,90 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B208" s="5" t="inlineStr">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D208" s="5" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E208" s="5" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr"/>
-      <c r="H208" s="5" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>32/32</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="9" t="inlineStr">
+        <is>
+          <t>A2-D2</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F209" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="9" t="inlineStr"/>
+      <c r="H209" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I208" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
-        <is>
-          <t>A2-D2</t>
-        </is>
-      </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E209" s="5" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr"/>
-      <c r="H209" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I209" s="5" t="inlineStr">
+      <c r="I209" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10804,258 +10840,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="5" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="6" t="inlineStr">
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I212" s="6" t="inlineStr">
+      <c r="I212" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
+      <c r="H213" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
+      <c r="H214" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
+      <c r="H217" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11861,86 +11897,90 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C235" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D235" s="5" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E235" s="5" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G235" s="5" t="inlineStr"/>
-      <c r="H235" s="5" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="9" t="inlineStr">
+        <is>
+          <t>A2-E1</t>
+        </is>
+      </c>
+      <c r="C236" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="9" t="inlineStr"/>
+      <c r="H236" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I235" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="5" t="inlineStr">
-        <is>
-          <t>A2-E1</t>
-        </is>
-      </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E236" s="5" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I236" s="5" t="inlineStr">
+      <c r="I236" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12041,258 +12081,258 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="6" t="inlineStr"/>
-      <c r="H239" s="6" t="inlineStr">
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I239" s="6" t="inlineStr">
+      <c r="I239" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr"/>
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I240" s="6" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr"/>
-      <c r="H241" s="6" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13098,86 +13138,90 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B262" s="5" t="inlineStr">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C262" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D262" s="5" t="inlineStr">
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E262" s="5" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F262" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G262" s="5" t="inlineStr"/>
-      <c r="H262" s="5" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>A2-E2</t>
+        </is>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="9" t="inlineStr"/>
+      <c r="H263" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I262" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
-        <is>
-          <t>A2-E2</t>
-        </is>
-      </c>
-      <c r="C263" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E263" s="5" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr"/>
-      <c r="H263" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I263" s="5" t="inlineStr">
+      <c r="I263" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13231,301 +13275,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr"/>
+      <c r="H265" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="6" t="inlineStr">
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="5" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="6" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr"/>
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I266" s="6" t="inlineStr">
+      <c r="I266" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr"/>
+      <c r="H267" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
+      <c r="I268" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14331,86 +14375,90 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B289" s="5" t="inlineStr">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C289" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D289" s="5" t="inlineStr">
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E289" s="5" t="inlineStr">
+      <c r="E289" s="2" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F289" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G289" s="5" t="inlineStr"/>
-      <c r="H289" s="5" t="inlineStr">
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>32/32</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="9" t="inlineStr">
+        <is>
+          <t>A2-F1</t>
+        </is>
+      </c>
+      <c r="C290" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E290" s="9" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F290" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="9" t="inlineStr"/>
+      <c r="H290" s="9" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I289" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="5" t="inlineStr">
-        <is>
-          <t>A2-F1</t>
-        </is>
-      </c>
-      <c r="C290" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E290" s="5" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="F290" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I290" s="5" t="inlineStr">
+      <c r="I290" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14511,258 +14559,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="6" t="inlineStr">
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="5" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="6" t="inlineStr">
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr"/>
+      <c r="H293" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I293" s="6" t="inlineStr">
+      <c r="I293" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="6" t="inlineStr">
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="6" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr"/>
+      <c r="H295" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14957,43 +15005,43 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
+      <c r="A303" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="9" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C303" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="5" t="inlineStr">
+      <c r="C303" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="5" t="inlineStr">
+      <c r="E303" s="9" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F303" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="5" t="inlineStr"/>
-      <c r="H303" s="5" t="inlineStr">
+      <c r="F303" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="9" t="inlineStr"/>
+      <c r="H303" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I303" s="5" t="inlineStr">
+      <c r="I303" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15564,86 +15612,90 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B316" s="5" t="inlineStr">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C316" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D316" s="5" t="inlineStr">
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E316" s="5" t="inlineStr">
+      <c r="E316" s="2" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G316" s="5" t="inlineStr"/>
-      <c r="H316" s="5" t="inlineStr">
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>29/29</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="inlineStr">
+        <is>
+          <t>A2-F2</t>
+        </is>
+      </c>
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E317" s="9" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="9" t="inlineStr"/>
+      <c r="H317" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I316" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
-        <is>
-          <t>A2-F2</t>
-        </is>
-      </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E317" s="5" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I317" s="5" t="inlineStr">
+      <c r="I317" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15744,258 +15796,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="6" t="inlineStr">
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="5" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="6" t="inlineStr"/>
-      <c r="H320" s="6" t="inlineStr">
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I320" s="6" t="inlineStr">
+      <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr"/>
+      <c r="H321" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr"/>
+      <c r="H325" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>21</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>21</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>21</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>20</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>20</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -2014,43 +2014,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2092,43 +2092,43 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2170,43 +2170,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2248,86 +2248,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2498,7 +2498,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2560,7 +2560,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2622,7 +2622,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3424,220 +3424,220 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>A2-A2</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>0/30</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>A2-A2</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4669,220 +4669,220 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>A2-B1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>A2-B1</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5914,220 +5914,220 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>A2-B2</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>A2-B2</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr"/>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6839,43 +6839,43 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E125" s="9" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I125" s="9" t="inlineStr">
+      <c r="I125" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -7155,220 +7155,220 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>A2-C1</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>0/31</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I133" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I134" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>A2-C1</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8080,43 +8080,43 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E152" s="9" t="inlineStr">
+      <c r="E152" s="5" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr"/>
-      <c r="H152" s="9" t="inlineStr">
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr"/>
+      <c r="H152" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I152" s="9" t="inlineStr">
+      <c r="I152" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -8396,220 +8396,220 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>A2-C2</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>0/29</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I159" s="5" t="inlineStr">
+      <c r="I160" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I160" s="5" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I161" s="5" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="inlineStr"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>A2-C2</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9462,43 +9462,43 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="9" t="inlineStr">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C182" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="9" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E182" s="9" t="inlineStr">
+      <c r="E182" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr"/>
-      <c r="H182" s="9" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr"/>
+      <c r="H182" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I182" s="9" t="inlineStr">
+      <c r="I182" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -9599,258 +9599,258 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E185" s="5" t="inlineStr">
+      <c r="E185" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr"/>
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I185" s="5" t="inlineStr">
+      <c r="I185" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="I186" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E187" s="5" t="inlineStr">
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="I187" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I188" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
+      <c r="E189" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I189" s="5" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="5" t="inlineStr">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E190" s="5" t="inlineStr">
+      <c r="E190" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F190" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10703,43 +10703,43 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="9" t="inlineStr">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C209" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="9" t="inlineStr">
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E209" s="9" t="inlineStr">
+      <c r="E209" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F209" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="9" t="inlineStr"/>
-      <c r="H209" s="9" t="inlineStr">
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr"/>
+      <c r="H209" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I209" s="9" t="inlineStr">
+      <c r="I209" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -10840,258 +10840,258 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E212" s="5" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr"/>
-      <c r="H212" s="5" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I212" s="5" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E213" s="5" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F213" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I213" s="5" t="inlineStr">
+      <c r="I213" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="5" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr">
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="I214" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E215" s="5" t="inlineStr">
+      <c r="E215" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F215" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="5" t="inlineStr"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I215" s="5" t="inlineStr">
+      <c r="I215" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="I216" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E217" s="5" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F217" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="5" t="inlineStr"/>
-      <c r="H217" s="5" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I217" s="5" t="inlineStr">
+      <c r="I217" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11944,43 +11944,43 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="9" t="inlineStr">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C236" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="9" t="inlineStr">
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E236" s="9" t="inlineStr">
+      <c r="E236" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F236" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="9" t="inlineStr"/>
-      <c r="H236" s="9" t="inlineStr">
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr"/>
+      <c r="H236" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I236" s="9" t="inlineStr">
+      <c r="I236" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -12081,258 +12081,258 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr"/>
-      <c r="H239" s="5" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr"/>
+      <c r="H239" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E240" s="5" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
-      <c r="H240" s="5" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="I240" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="5" t="inlineStr">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E241" s="5" t="inlineStr">
+      <c r="E241" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="5" t="inlineStr"/>
-      <c r="H241" s="5" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr"/>
+      <c r="H241" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I241" s="5" t="inlineStr">
+      <c r="I241" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C242" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="5" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="5" t="inlineStr"/>
-      <c r="H243" s="5" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr"/>
+      <c r="H243" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C244" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr"/>
-      <c r="H244" s="5" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13185,43 +13185,43 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C263" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="9" t="inlineStr">
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E263" s="9" t="inlineStr">
+      <c r="E263" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F263" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="9" t="inlineStr"/>
-      <c r="H263" s="9" t="inlineStr">
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr"/>
+      <c r="H263" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I263" s="9" t="inlineStr">
+      <c r="I263" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13275,301 +13275,301 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E265" s="9" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F265" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="9" t="inlineStr"/>
-      <c r="H265" s="9" t="inlineStr">
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr"/>
+      <c r="H265" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I265" s="9" t="inlineStr">
+      <c r="I265" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="5" t="inlineStr">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C266" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E266" s="5" t="inlineStr">
+      <c r="E266" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="5" t="inlineStr"/>
-      <c r="H266" s="5" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr"/>
+      <c r="H266" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I266" s="5" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr"/>
+      <c r="H267" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I267" s="5" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr"/>
+      <c r="H268" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I268" s="5" t="inlineStr">
+      <c r="I268" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="5" t="inlineStr">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C269" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E269" s="5" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="5" t="inlineStr"/>
-      <c r="H269" s="5" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr"/>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I269" s="5" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr"/>
+      <c r="H270" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="5" t="inlineStr">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C271" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E271" s="5" t="inlineStr">
+      <c r="E271" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F271" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="inlineStr"/>
-      <c r="H271" s="5" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr"/>
+      <c r="H271" s="6" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I271" s="5" t="inlineStr">
+      <c r="I271" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14422,43 +14422,43 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="9" t="inlineStr">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C290" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="9" t="inlineStr">
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E290" s="9" t="inlineStr">
+      <c r="E290" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F290" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="9" t="inlineStr"/>
-      <c r="H290" s="9" t="inlineStr">
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="inlineStr"/>
+      <c r="H290" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I290" s="9" t="inlineStr">
+      <c r="I290" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -14559,258 +14559,258 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr"/>
+      <c r="H293" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I293" s="5" t="inlineStr">
+      <c r="I293" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="5" t="inlineStr">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C294" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E294" s="5" t="inlineStr">
+      <c r="E294" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F294" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="5" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="6" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="I294" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E295" s="5" t="inlineStr">
+      <c r="E295" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F295" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="5" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr"/>
+      <c r="H295" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I295" s="5" t="inlineStr">
+      <c r="I295" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="5" t="inlineStr">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C296" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E296" s="5" t="inlineStr">
+      <c r="E296" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F296" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="5" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E297" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr"/>
-      <c r="H297" s="5" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr"/>
+      <c r="H297" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I297" s="5" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C298" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E298" s="5" t="inlineStr">
+      <c r="E298" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="5" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15005,43 +15005,43 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="9" t="inlineStr">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C303" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="9" t="inlineStr">
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="9" t="inlineStr">
+      <c r="E303" s="5" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F303" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="9" t="inlineStr"/>
-      <c r="H303" s="9" t="inlineStr">
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr"/>
+      <c r="H303" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I303" s="9" t="inlineStr">
+      <c r="I303" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15659,43 +15659,43 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="9" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C317" s="9" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="9" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E317" s="9" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F317" s="9" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="9" t="inlineStr"/>
-      <c r="H317" s="9" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I317" s="9" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15796,258 +15796,258 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="5" t="inlineStr">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C320" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E320" s="5" t="inlineStr">
+      <c r="E320" s="6" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F320" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="5" t="inlineStr"/>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="6" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="I320" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="5" t="inlineStr">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C321" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="C321" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E321" s="5" t="inlineStr">
+      <c r="E321" s="6" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F321" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="inlineStr"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="6" t="inlineStr"/>
+      <c r="H321" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I321" s="5" t="inlineStr">
+      <c r="I321" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="5" t="inlineStr">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C322" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E322" s="5" t="inlineStr">
+      <c r="E322" s="6" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F322" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="5" t="inlineStr"/>
-      <c r="H322" s="5" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="6" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I322" s="5" t="inlineStr">
+      <c r="I322" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C323" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E323" s="5" t="inlineStr">
+      <c r="E323" s="6" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F323" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="5" t="inlineStr"/>
-      <c r="H323" s="5" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="6" t="inlineStr"/>
+      <c r="H323" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I323" s="5" t="inlineStr">
+      <c r="I323" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E324" s="5" t="inlineStr">
+      <c r="E324" s="6" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F324" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="5" t="inlineStr"/>
-      <c r="H324" s="5" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="6" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E325" s="5" t="inlineStr">
+      <c r="E325" s="6" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F325" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="5" t="inlineStr"/>
-      <c r="H325" s="5" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="6" t="inlineStr"/>
+      <c r="H325" s="6" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="6" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>21</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>21</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>21</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>20</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>20</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2014,45 +2014,45 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -3429,45 +3429,45 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4674,45 +4674,45 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5919,45 +5919,45 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr"/>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7160,45 +7160,45 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8401,45 +8401,45 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="6" t="inlineStr"/>
-      <c r="H159" s="6" t="inlineStr">
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I159" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>78.7%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.7%</t>
         </is>
       </c>
     </row>
@@ -2014,45 +2014,49 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -3429,45 +3433,49 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3830,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3963,7 +3971,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4386,7 +4394,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>27/31</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -4631,88 +4639,96 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5647,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>22/28</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5919,45 +5935,49 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6839,45 +6859,49 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>13/31</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7160,45 +7184,49 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I132" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8401,45 +8429,49 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I159" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>21/31</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -8108,45 +8108,49 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr"/>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1834,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -1916,22 +1916,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -1994,22 +1994,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -2076,22 +2076,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -2154,22 +2154,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -2232,22 +2232,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>74.8%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -9498,45 +9498,49 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E182" s="5" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10739,45 +10743,49 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D209" s="5" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E209" s="5" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F209" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G209" s="5" t="inlineStr"/>
-      <c r="H209" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I209" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>29/32</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11980,45 +11988,49 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C236" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E236" s="5" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I236" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13221,45 +13233,49 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B263" s="5" t="inlineStr">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C263" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E263" s="5" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G263" s="5" t="inlineStr"/>
-      <c r="H263" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I263" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14458,45 +14474,49 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B290" s="5" t="inlineStr">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C290" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D290" s="5" t="inlineStr">
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E290" s="5" t="inlineStr">
+      <c r="E290" s="2" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F290" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="5" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I290" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>2/32</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15695,45 +15715,49 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B317" s="5" t="inlineStr">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C317" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E317" s="5" t="inlineStr">
+      <c r="E317" s="2" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F317" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G317" s="5" t="inlineStr"/>
-      <c r="H317" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I317" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>22</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>23</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>22</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>22</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         <v>22</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -2096,45 +2096,45 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -3480,45 +3480,45 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4733,45 +4733,45 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5982,45 +5982,45 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7231,45 +7231,45 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8480,45 +8480,45 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
+      <c r="H160" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>27</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -1670,17 +1670,17 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.5%</t>
         </is>
       </c>
     </row>
@@ -2096,45 +2096,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -3480,45 +3484,49 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4733,45 +4741,49 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5982,45 +5994,49 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7231,45 +7247,49 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I133" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8480,45 +8500,49 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E160" s="5" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I160" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>83.0%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -1834,22 +1834,22 @@
         <v>27</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -1916,22 +1916,22 @@
         <v>27</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
     </row>
@@ -1994,22 +1994,22 @@
         <v>27</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -2076,22 +2076,22 @@
         <v>27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -2158,22 +2158,22 @@
         <v>27</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>73.2%</t>
         </is>
       </c>
     </row>
@@ -2236,22 +2236,22 @@
         <v>27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -9663,45 +9663,49 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I185" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10908,45 +10912,49 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="6" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I212" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>28/32</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12153,45 +12161,49 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G239" s="6" t="inlineStr"/>
-      <c r="H239" s="6" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I239" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13394,45 +13406,49 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D266" s="6" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="6" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I266" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14639,45 +14655,49 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C293" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D293" s="6" t="inlineStr">
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="6" t="inlineStr">
-        <is>
-          <t>0/32</t>
-        </is>
-      </c>
-      <c r="I293" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>29/32</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15880,45 +15900,49 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D320" s="6" t="inlineStr">
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G320" s="6" t="inlineStr"/>
-      <c r="H320" s="6" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I320" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -58,14 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFB6C1"/>
-        <bgColor rgb="00FFB6C1"/>
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
+        <fgColor rgb="00FFB6C1"/>
+        <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,16 +96,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>27</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>27</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1588,22 @@
         <v>27</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.5%</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1752,22 @@
         <v>27</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
     </row>
@@ -1936,45 +1936,49 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -2178,43 +2182,43 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2256,86 +2260,86 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A2-A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -2506,7 +2510,7 @@
           <t>Recorded</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
@@ -2568,7 +2572,7 @@
           <t>Not Recorded</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2630,7 +2634,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -3394,45 +3398,49 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>0/30</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3531,129 +3539,129 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>A2-A2</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0/30</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4684,7 +4692,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>27/31</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4788,129 +4796,129 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>A2-B1</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5904,45 +5912,49 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -6041,129 +6053,129 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>A2-B2</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7157,45 +7169,49 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>0/31</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>11/31</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7294,129 +7310,129 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>A2-C1</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -8410,45 +8426,49 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E158" s="5" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="inlineStr"/>
-      <c r="H158" s="5" t="inlineStr">
-        <is>
-          <t>0/29</t>
-        </is>
-      </c>
-      <c r="I158" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -8547,129 +8567,129 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="5" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr">
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I161" s="6" t="inlineStr">
+      <c r="I161" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="5" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I162" s="6" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A2-C2</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I163" s="6" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9710,215 +9730,215 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr"/>
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A2-D1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr"/>
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -10959,215 +10979,215 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr">
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr"/>
+      <c r="H213" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr"/>
-      <c r="H214" s="6" t="inlineStr">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr"/>
+      <c r="H214" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G215" s="6" t="inlineStr"/>
-      <c r="H215" s="6" t="inlineStr">
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr"/>
+      <c r="H215" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I215" s="6" t="inlineStr">
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr"/>
-      <c r="H216" s="6" t="inlineStr">
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr"/>
+      <c r="H216" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I216" s="6" t="inlineStr">
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>A2-D2</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G217" s="6" t="inlineStr"/>
-      <c r="H217" s="6" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr"/>
+      <c r="H217" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I217" s="6" t="inlineStr">
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -12208,215 +12228,215 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr"/>
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I240" s="6" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr"/>
-      <c r="H241" s="6" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I241" s="6" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G242" s="6" t="inlineStr"/>
-      <c r="H242" s="6" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I242" s="6" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G243" s="6" t="inlineStr"/>
-      <c r="H243" s="6" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I243" s="6" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A2-E1</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr"/>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13363,43 +13383,43 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B265" s="9" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E265" s="5" t="inlineStr">
+      <c r="E265" s="9" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="F265" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G265" s="5" t="inlineStr"/>
-      <c r="H265" s="5" t="inlineStr">
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr"/>
+      <c r="H265" s="9" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I265" s="5" t="inlineStr">
+      <c r="I265" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -13453,215 +13473,215 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D267" s="6" t="inlineStr">
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="6" t="inlineStr">
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr"/>
+      <c r="H267" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I267" s="6" t="inlineStr">
+      <c r="I267" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
+      <c r="I268" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
+      <c r="I269" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D270" s="6" t="inlineStr">
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr"/>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I270" s="6" t="inlineStr">
+      <c r="I270" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>A2-E2</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/31</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
+      <c r="I271" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14702,215 +14722,215 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D295" s="6" t="inlineStr">
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="6" t="inlineStr">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr"/>
+      <c r="H295" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D296" s="6" t="inlineStr">
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B297" s="6" t="inlineStr">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C297" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D297" s="6" t="inlineStr">
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="6" t="inlineStr">
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr"/>
+      <c r="H297" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
         <is>
           <t>A2-F1</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="5" t="inlineStr">
         <is>
           <t>0/32</t>
         </is>
       </c>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15105,43 +15125,43 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
+      <c r="A303" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B303" s="9" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C303" s="5" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D303" s="5" t="inlineStr">
+      <c r="C303" s="9" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E303" s="5" t="inlineStr">
+      <c r="E303" s="9" t="inlineStr">
         <is>
           <t>04/03/2026</t>
         </is>
       </c>
-      <c r="F303" s="5" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G303" s="5" t="inlineStr"/>
-      <c r="H303" s="5" t="inlineStr">
+      <c r="F303" s="9" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G303" s="9" t="inlineStr"/>
+      <c r="H303" s="9" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I303" s="5" t="inlineStr">
+      <c r="I303" s="9" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
@@ -15947,215 +15967,215 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C321" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D321" s="6" t="inlineStr">
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G321" s="6" t="inlineStr"/>
-      <c r="H321" s="6" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr"/>
+      <c r="H321" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I321" s="6" t="inlineStr">
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D322" s="6" t="inlineStr">
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G322" s="6" t="inlineStr"/>
-      <c r="H322" s="6" t="inlineStr">
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I322" s="6" t="inlineStr">
+      <c r="I322" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B323" s="6" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C323" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D323" s="6" t="inlineStr">
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G323" s="6" t="inlineStr"/>
-      <c r="H323" s="6" t="inlineStr">
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr"/>
+      <c r="H323" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I323" s="6" t="inlineStr">
+      <c r="I323" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B324" s="6" t="inlineStr">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C324" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D324" s="6" t="inlineStr">
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G324" s="6" t="inlineStr"/>
-      <c r="H324" s="6" t="inlineStr">
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I324" s="6" t="inlineStr">
+      <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B325" s="6" t="inlineStr">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>A2-F2</t>
         </is>
       </c>
-      <c r="C325" s="6" t="inlineStr">
-        <is>
-          <t>GENERAL SURGERY</t>
-        </is>
-      </c>
-      <c r="D325" s="6" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>GENERAL SURGERY</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="G325" s="6" t="inlineStr"/>
-      <c r="H325" s="6" t="inlineStr">
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr"/>
+      <c r="H325" s="5" t="inlineStr">
         <is>
           <t>0/29</t>
         </is>
       </c>
-      <c r="I325" s="6" t="inlineStr">
+      <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>18/31</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>23/29</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026, 2526</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15247,7 +15247,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>Miss Dina Nasr</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A2_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2526</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Miss Dina Nasr</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+